--- a/assets/SCC_Log_Frame.xlsx
+++ b/assets/SCC_Log_Frame.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ZN108\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{872D61B9-5FB1-4DB2-B0F9-DF3455AFE673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D85848-A7D6-48C4-A6BB-EEE28412A0C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-870" windowWidth="29040" windowHeight="15720" tabRatio="885" xr2:uid="{00AD3E43-05CC-45FC-A0FF-E89A67A13665}"/>
   </bookViews>
@@ -2213,7 +2213,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3109,7 +3109,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="268">
+  <cellXfs count="267">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3754,36 +3754,129 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3795,102 +3888,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -4277,7 +4274,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0FD833-DA25-49DC-8173-D7C8564C9878}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:BF152"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="43.5" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="43.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="128" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
@@ -4312,7 +4309,7 @@
     <col min="43" max="44" width="9.109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" ht="6.6" hidden="1" customHeight="1">
+    <row r="1" spans="1:58" ht="6.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="122"/>
       <c r="B1" s="28"/>
       <c r="C1" s="76"/>
@@ -4372,7 +4369,7 @@
       <c r="BE1" s="116"/>
       <c r="BF1" s="116"/>
     </row>
-    <row r="2" spans="1:58" ht="21.6" hidden="1" customHeight="1">
+    <row r="2" spans="1:58" ht="21.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="28"/>
       <c r="B2" s="28"/>
       <c r="C2" s="76"/>
@@ -4432,7 +4429,7 @@
       <c r="BE2" s="116"/>
       <c r="BF2" s="116"/>
     </row>
-    <row r="3" spans="1:58" ht="19.2" customHeight="1">
+    <row r="3" spans="1:58" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="197" t="s">
         <v>2</v>
       </c>
@@ -4500,7 +4497,7 @@
       <c r="BE3" s="116"/>
       <c r="BF3" s="116"/>
     </row>
-    <row r="4" spans="1:58" ht="15" customHeight="1">
+    <row r="4" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="199" t="s">
         <v>3</v>
       </c>
@@ -4564,7 +4561,7 @@
       <c r="BE4" s="116"/>
       <c r="BF4" s="116"/>
     </row>
-    <row r="5" spans="1:58" ht="20.25" customHeight="1" thickBot="1">
+    <row r="5" spans="1:58" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="200" t="s">
         <v>5</v>
       </c>
@@ -4628,60 +4625,60 @@
       <c r="BE5" s="116"/>
       <c r="BF5" s="116"/>
     </row>
-    <row r="6" spans="1:58" ht="24.6" customHeight="1">
-      <c r="A6" s="236" t="s">
+    <row r="6" spans="1:58" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="232" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="155"/>
       <c r="C6" s="154"/>
-      <c r="D6" s="238" t="s">
+      <c r="D6" s="223" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="239"/>
-      <c r="F6" s="239"/>
-      <c r="G6" s="240"/>
-      <c r="H6" s="241" t="s">
+      <c r="E6" s="224"/>
+      <c r="F6" s="224"/>
+      <c r="G6" s="225"/>
+      <c r="H6" s="250" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="242"/>
-      <c r="J6" s="242"/>
-      <c r="K6" s="242"/>
-      <c r="L6" s="242"/>
-      <c r="M6" s="242"/>
-      <c r="N6" s="242"/>
-      <c r="O6" s="242"/>
-      <c r="P6" s="242"/>
-      <c r="Q6" s="243"/>
-      <c r="R6" s="244" t="s">
+      <c r="I6" s="251"/>
+      <c r="J6" s="251"/>
+      <c r="K6" s="251"/>
+      <c r="L6" s="251"/>
+      <c r="M6" s="251"/>
+      <c r="N6" s="251"/>
+      <c r="O6" s="251"/>
+      <c r="P6" s="251"/>
+      <c r="Q6" s="252"/>
+      <c r="R6" s="253" t="s">
         <v>10</v>
       </c>
-      <c r="S6" s="244"/>
-      <c r="T6" s="244"/>
-      <c r="U6" s="244"/>
-      <c r="V6" s="244"/>
-      <c r="W6" s="244"/>
-      <c r="X6" s="244"/>
-      <c r="Y6" s="244"/>
-      <c r="Z6" s="244"/>
-      <c r="AA6" s="241"/>
-      <c r="AB6" s="244" t="s">
+      <c r="S6" s="253"/>
+      <c r="T6" s="253"/>
+      <c r="U6" s="253"/>
+      <c r="V6" s="253"/>
+      <c r="W6" s="253"/>
+      <c r="X6" s="253"/>
+      <c r="Y6" s="253"/>
+      <c r="Z6" s="253"/>
+      <c r="AA6" s="250"/>
+      <c r="AB6" s="253" t="s">
         <v>469</v>
       </c>
-      <c r="AC6" s="244"/>
-      <c r="AD6" s="244"/>
-      <c r="AE6" s="244"/>
-      <c r="AF6" s="244"/>
-      <c r="AG6" s="244"/>
-      <c r="AH6" s="244"/>
-      <c r="AI6" s="244"/>
-      <c r="AJ6" s="244"/>
-      <c r="AK6" s="241"/>
+      <c r="AC6" s="253"/>
+      <c r="AD6" s="253"/>
+      <c r="AE6" s="253"/>
+      <c r="AF6" s="253"/>
+      <c r="AG6" s="253"/>
+      <c r="AH6" s="253"/>
+      <c r="AI6" s="253"/>
+      <c r="AJ6" s="253"/>
+      <c r="AK6" s="250"/>
       <c r="AL6" s="254" t="s">
         <v>11</v>
       </c>
       <c r="AM6" s="255"/>
       <c r="AN6" s="256"/>
-      <c r="AO6" s="260" t="s">
+      <c r="AO6" s="244" t="s">
         <v>12</v>
       </c>
       <c r="AP6" s="114"/>
@@ -4702,66 +4699,66 @@
       <c r="BE6" s="116"/>
       <c r="BF6" s="116"/>
     </row>
-    <row r="7" spans="1:58" ht="16.2" customHeight="1">
-      <c r="A7" s="237"/>
+    <row r="7" spans="1:58" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="233"/>
       <c r="B7" s="153" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="262" t="s">
+      <c r="D7" s="226" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="263"/>
-      <c r="F7" s="263"/>
-      <c r="G7" s="264"/>
+      <c r="E7" s="227"/>
+      <c r="F7" s="227"/>
+      <c r="G7" s="228"/>
       <c r="H7" s="246" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="265"/>
-      <c r="J7" s="265"/>
-      <c r="K7" s="265"/>
-      <c r="L7" s="266"/>
+      <c r="I7" s="247"/>
+      <c r="J7" s="247"/>
+      <c r="K7" s="247"/>
+      <c r="L7" s="248"/>
       <c r="M7" s="246" t="s">
         <v>1</v>
       </c>
-      <c r="N7" s="265"/>
-      <c r="O7" s="265"/>
-      <c r="P7" s="265"/>
-      <c r="Q7" s="266"/>
-      <c r="R7" s="245" t="s">
+      <c r="N7" s="247"/>
+      <c r="O7" s="247"/>
+      <c r="P7" s="247"/>
+      <c r="Q7" s="248"/>
+      <c r="R7" s="249" t="s">
         <v>16</v>
       </c>
-      <c r="S7" s="245"/>
-      <c r="T7" s="245"/>
-      <c r="U7" s="245"/>
-      <c r="V7" s="245"/>
-      <c r="W7" s="245" t="s">
+      <c r="S7" s="249"/>
+      <c r="T7" s="249"/>
+      <c r="U7" s="249"/>
+      <c r="V7" s="249"/>
+      <c r="W7" s="249" t="s">
         <v>1</v>
       </c>
-      <c r="X7" s="245"/>
-      <c r="Y7" s="245"/>
-      <c r="Z7" s="245"/>
+      <c r="X7" s="249"/>
+      <c r="Y7" s="249"/>
+      <c r="Z7" s="249"/>
       <c r="AA7" s="246"/>
-      <c r="AB7" s="245" t="s">
+      <c r="AB7" s="249" t="s">
         <v>16</v>
       </c>
-      <c r="AC7" s="245"/>
-      <c r="AD7" s="245"/>
-      <c r="AE7" s="245"/>
-      <c r="AF7" s="245"/>
-      <c r="AG7" s="245" t="s">
+      <c r="AC7" s="249"/>
+      <c r="AD7" s="249"/>
+      <c r="AE7" s="249"/>
+      <c r="AF7" s="249"/>
+      <c r="AG7" s="249" t="s">
         <v>1</v>
       </c>
-      <c r="AH7" s="245"/>
-      <c r="AI7" s="245"/>
-      <c r="AJ7" s="245"/>
+      <c r="AH7" s="249"/>
+      <c r="AI7" s="249"/>
+      <c r="AJ7" s="249"/>
       <c r="AK7" s="246"/>
       <c r="AL7" s="257"/>
       <c r="AM7" s="258"/>
       <c r="AN7" s="259"/>
-      <c r="AO7" s="261"/>
+      <c r="AO7" s="245"/>
       <c r="AP7" s="114"/>
       <c r="AQ7" s="114"/>
       <c r="AR7" s="114"/>
@@ -4780,8 +4777,8 @@
       <c r="BE7" s="116"/>
       <c r="BF7" s="116"/>
     </row>
-    <row r="8" spans="1:58" ht="21.6" customHeight="1" thickBot="1">
-      <c r="A8" s="237"/>
+    <row r="8" spans="1:58" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="233"/>
       <c r="B8" s="1"/>
       <c r="C8" s="2"/>
       <c r="D8" s="5" t="s">
@@ -4895,7 +4892,7 @@
       <c r="AN8" s="157" t="s">
         <v>21</v>
       </c>
-      <c r="AO8" s="261"/>
+      <c r="AO8" s="245"/>
       <c r="AP8" s="115"/>
       <c r="AQ8" s="115"/>
       <c r="AR8" s="115"/>
@@ -4914,8 +4911,8 @@
       <c r="BE8" s="116"/>
       <c r="BF8" s="116"/>
     </row>
-    <row r="9" spans="1:58" ht="36.75" customHeight="1" thickBot="1">
-      <c r="A9" s="247" t="s">
+    <row r="9" spans="1:58" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="237" t="s">
         <v>23</v>
       </c>
       <c r="B9" s="15" t="s">
@@ -5013,8 +5010,8 @@
       <c r="BE9" s="116"/>
       <c r="BF9" s="116"/>
     </row>
-    <row r="10" spans="1:58" ht="28.95" customHeight="1" thickBot="1">
-      <c r="A10" s="248"/>
+    <row r="10" spans="1:58" ht="28.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="238"/>
       <c r="B10" s="24" t="s">
         <v>27</v>
       </c>
@@ -5107,8 +5104,8 @@
       <c r="BE10" s="116"/>
       <c r="BF10" s="116"/>
     </row>
-    <row r="11" spans="1:58" ht="44.25" customHeight="1">
-      <c r="A11" s="249"/>
+    <row r="11" spans="1:58" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="239"/>
       <c r="B11" s="24" t="s">
         <v>30</v>
       </c>
@@ -5203,8 +5200,8 @@
       <c r="BE11" s="116"/>
       <c r="BF11" s="116"/>
     </row>
-    <row r="12" spans="1:58" ht="28.95" customHeight="1">
-      <c r="A12" s="250"/>
+    <row r="12" spans="1:58" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="240"/>
       <c r="B12" s="16" t="s">
         <v>33</v>
       </c>
@@ -5299,11 +5296,11 @@
       <c r="BE12" s="116"/>
       <c r="BF12" s="116"/>
     </row>
-    <row r="13" spans="1:58" ht="15.6" customHeight="1">
-      <c r="A13" s="251" t="s">
+    <row r="13" spans="1:58" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="230" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="252"/>
+      <c r="B13" s="231"/>
       <c r="C13" s="97"/>
       <c r="D13" s="5" t="s">
         <v>17</v>
@@ -5369,8 +5366,8 @@
       <c r="BE13" s="116"/>
       <c r="BF13" s="116"/>
     </row>
-    <row r="14" spans="1:58" ht="85.2" customHeight="1">
-      <c r="A14" s="253" t="s">
+    <row r="14" spans="1:58" ht="85.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="236" t="s">
         <v>37</v>
       </c>
       <c r="B14" s="86" t="s">
@@ -5467,8 +5464,8 @@
       <c r="BE14" s="116"/>
       <c r="BF14" s="116"/>
     </row>
-    <row r="15" spans="1:58" ht="51.75" customHeight="1">
-      <c r="A15" s="222"/>
+    <row r="15" spans="1:58" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="234"/>
       <c r="B15" s="29" t="s">
         <v>41</v>
       </c>
@@ -5563,8 +5560,8 @@
       <c r="BE15" s="116"/>
       <c r="BF15" s="116"/>
     </row>
-    <row r="16" spans="1:58" ht="36">
-      <c r="A16" s="222"/>
+    <row r="16" spans="1:58" ht="36" x14ac:dyDescent="0.3">
+      <c r="A16" s="234"/>
       <c r="B16" s="29" t="s">
         <v>44</v>
       </c>
@@ -5659,8 +5656,8 @@
       <c r="BE16" s="116"/>
       <c r="BF16" s="116"/>
     </row>
-    <row r="17" spans="1:58" ht="61.2" customHeight="1">
-      <c r="A17" s="222" t="s">
+    <row r="17" spans="1:58" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="234" t="s">
         <v>47</v>
       </c>
       <c r="B17" s="29" t="s">
@@ -5757,8 +5754,8 @@
       <c r="BE17" s="116"/>
       <c r="BF17" s="116"/>
     </row>
-    <row r="18" spans="1:58" ht="48.75" customHeight="1">
-      <c r="A18" s="222"/>
+    <row r="18" spans="1:58" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="234"/>
       <c r="B18" s="35" t="s">
         <v>51</v>
       </c>
@@ -5853,8 +5850,8 @@
       <c r="BE18" s="116"/>
       <c r="BF18" s="116"/>
     </row>
-    <row r="19" spans="1:58" ht="50.4" customHeight="1">
-      <c r="A19" s="222"/>
+    <row r="19" spans="1:58" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="234"/>
       <c r="B19" s="29" t="s">
         <v>54</v>
       </c>
@@ -5949,8 +5946,8 @@
       <c r="BE19" s="116"/>
       <c r="BF19" s="116"/>
     </row>
-    <row r="20" spans="1:58" ht="51.6" customHeight="1">
-      <c r="A20" s="222"/>
+    <row r="20" spans="1:58" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="234"/>
       <c r="B20" s="29" t="s">
         <v>57</v>
       </c>
@@ -6045,8 +6042,8 @@
       <c r="BE20" s="116"/>
       <c r="BF20" s="116"/>
     </row>
-    <row r="21" spans="1:58" ht="43.2" customHeight="1">
-      <c r="A21" s="222"/>
+    <row r="21" spans="1:58" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="234"/>
       <c r="B21" s="29" t="s">
         <v>60</v>
       </c>
@@ -6141,8 +6138,8 @@
       <c r="BE21" s="116"/>
       <c r="BF21" s="116"/>
     </row>
-    <row r="22" spans="1:58" ht="57" customHeight="1">
-      <c r="A22" s="222" t="s">
+    <row r="22" spans="1:58" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="234" t="s">
         <v>63</v>
       </c>
       <c r="B22" s="37" t="s">
@@ -6246,8 +6243,8 @@
       <c r="BE22" s="116"/>
       <c r="BF22" s="116"/>
     </row>
-    <row r="23" spans="1:58" ht="51" customHeight="1">
-      <c r="A23" s="231"/>
+    <row r="23" spans="1:58" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="235"/>
       <c r="B23" s="37" t="s">
         <v>67</v>
       </c>
@@ -6345,7 +6342,7 @@
       <c r="BE23" s="116"/>
       <c r="BF23" s="116"/>
     </row>
-    <row r="24" spans="1:58" ht="138.6" customHeight="1">
+    <row r="24" spans="1:58" ht="138.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="29" t="s">
         <v>70</v>
       </c>
@@ -6450,7 +6447,7 @@
       <c r="BE24" s="116"/>
       <c r="BF24" s="116"/>
     </row>
-    <row r="25" spans="1:58" ht="98.4" customHeight="1">
+    <row r="25" spans="1:58" ht="98.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="39" t="s">
         <v>74</v>
       </c>
@@ -6557,8 +6554,8 @@
       <c r="BE25" s="116"/>
       <c r="BF25" s="116"/>
     </row>
-    <row r="26" spans="1:58" ht="36">
-      <c r="A26" s="226" t="s">
+    <row r="26" spans="1:58" ht="36" x14ac:dyDescent="0.3">
+      <c r="A26" s="229" t="s">
         <v>78</v>
       </c>
       <c r="B26" s="29" t="s">
@@ -6670,8 +6667,8 @@
       <c r="BE26" s="116"/>
       <c r="BF26" s="116"/>
     </row>
-    <row r="27" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A27" s="226"/>
+    <row r="27" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="229"/>
       <c r="B27" s="29" t="s">
         <v>82</v>
       </c>
@@ -6781,8 +6778,8 @@
       <c r="BE27" s="116"/>
       <c r="BF27" s="116"/>
     </row>
-    <row r="28" spans="1:58" ht="44.4" customHeight="1">
-      <c r="A28" s="226"/>
+    <row r="28" spans="1:58" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="229"/>
       <c r="B28" s="29" t="s">
         <v>84</v>
       </c>
@@ -6894,8 +6891,8 @@
       <c r="BE28" s="116"/>
       <c r="BF28" s="116"/>
     </row>
-    <row r="29" spans="1:58" ht="58.95" customHeight="1">
-      <c r="A29" s="226"/>
+    <row r="29" spans="1:58" ht="58.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="229"/>
       <c r="B29" s="29" t="s">
         <v>87</v>
       </c>
@@ -7003,7 +7000,7 @@
       <c r="BE29" s="116"/>
       <c r="BF29" s="116"/>
     </row>
-    <row r="30" spans="1:58" ht="97.2" customHeight="1">
+    <row r="30" spans="1:58" ht="97.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="74" t="s">
         <v>90</v>
       </c>
@@ -7110,7 +7107,7 @@
       <c r="BE30" s="116"/>
       <c r="BF30" s="116"/>
     </row>
-    <row r="31" spans="1:58" ht="84" customHeight="1">
+    <row r="31" spans="1:58" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="112" t="s">
         <v>94</v>
       </c>
@@ -7225,7 +7222,7 @@
       <c r="BE31" s="116"/>
       <c r="BF31" s="116"/>
     </row>
-    <row r="32" spans="1:58" ht="43.5" customHeight="1">
+    <row r="32" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="74" t="s">
         <v>97</v>
       </c>
@@ -7344,7 +7341,7 @@
       <c r="BE32" s="116"/>
       <c r="BF32" s="116"/>
     </row>
-    <row r="33" spans="1:58" ht="43.5" customHeight="1">
+    <row r="33" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="123" t="s">
         <v>101</v>
       </c>
@@ -7447,11 +7444,11 @@
       <c r="BE33" s="116"/>
       <c r="BF33" s="116"/>
     </row>
-    <row r="34" spans="1:58" ht="12" customHeight="1">
-      <c r="A34" s="228" t="s">
+    <row r="34" spans="1:58" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="242" t="s">
         <v>106</v>
       </c>
-      <c r="B34" s="229"/>
+      <c r="B34" s="243"/>
       <c r="C34" s="92"/>
       <c r="D34" s="5" t="s">
         <v>17</v>
@@ -7517,8 +7514,8 @@
       <c r="BE34" s="116"/>
       <c r="BF34" s="116"/>
     </row>
-    <row r="35" spans="1:58" ht="48">
-      <c r="A35" s="225" t="s">
+    <row r="35" spans="1:58" ht="48" x14ac:dyDescent="0.3">
+      <c r="A35" s="241" t="s">
         <v>107</v>
       </c>
       <c r="B35" s="86" t="s">
@@ -7615,8 +7612,8 @@
       <c r="BE35" s="116"/>
       <c r="BF35" s="116"/>
     </row>
-    <row r="36" spans="1:58" ht="48">
-      <c r="A36" s="231"/>
+    <row r="36" spans="1:58" ht="48" x14ac:dyDescent="0.3">
+      <c r="A36" s="235"/>
       <c r="B36" s="29" t="s">
         <v>111</v>
       </c>
@@ -7711,8 +7708,8 @@
       <c r="BE36" s="116"/>
       <c r="BF36" s="116"/>
     </row>
-    <row r="37" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A37" s="232" t="s">
+    <row r="37" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="263" t="s">
         <v>114</v>
       </c>
       <c r="B37" s="29" t="s">
@@ -7809,8 +7806,8 @@
       <c r="BE37" s="116"/>
       <c r="BF37" s="116"/>
     </row>
-    <row r="38" spans="1:58" ht="30.6" customHeight="1">
-      <c r="A38" s="233"/>
+    <row r="38" spans="1:58" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="264"/>
       <c r="B38" s="29" t="s">
         <v>118</v>
       </c>
@@ -7905,8 +7902,8 @@
       <c r="BE38" s="116"/>
       <c r="BF38" s="116"/>
     </row>
-    <row r="39" spans="1:58" ht="30.6" customHeight="1">
-      <c r="A39" s="234"/>
+    <row r="39" spans="1:58" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="265"/>
       <c r="B39" s="29" t="s">
         <v>121</v>
       </c>
@@ -8001,7 +7998,7 @@
       <c r="BE39" s="116"/>
       <c r="BF39" s="116"/>
     </row>
-    <row r="40" spans="1:58" ht="58.95" customHeight="1">
+    <row r="40" spans="1:58" ht="58.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="124" t="s">
         <v>124</v>
       </c>
@@ -8110,7 +8107,7 @@
       <c r="BE40" s="116"/>
       <c r="BF40" s="116"/>
     </row>
-    <row r="41" spans="1:58" ht="51.6" customHeight="1">
+    <row r="41" spans="1:58" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="112" t="s">
         <v>128</v>
       </c>
@@ -8217,8 +8214,8 @@
       <c r="BE41" s="116"/>
       <c r="BF41" s="116"/>
     </row>
-    <row r="42" spans="1:58" ht="51.75" customHeight="1">
-      <c r="A42" s="227" t="s">
+    <row r="42" spans="1:58" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="222" t="s">
         <v>132</v>
       </c>
       <c r="B42" s="29" t="s">
@@ -8287,7 +8284,7 @@
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
-      <c r="AB42" s="267">
+      <c r="AB42" s="36">
         <v>6</v>
       </c>
       <c r="AC42" s="36"/>
@@ -8346,8 +8343,8 @@
       <c r="BE42" s="116"/>
       <c r="BF42" s="116"/>
     </row>
-    <row r="43" spans="1:58" ht="54.6" customHeight="1">
-      <c r="A43" s="227"/>
+    <row r="43" spans="1:58" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="222"/>
       <c r="B43" s="29" t="s">
         <v>136</v>
       </c>
@@ -8473,8 +8470,8 @@
       <c r="BE43" s="116"/>
       <c r="BF43" s="116"/>
     </row>
-    <row r="44" spans="1:58" ht="41.4" customHeight="1">
-      <c r="A44" s="227"/>
+    <row r="44" spans="1:58" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="222"/>
       <c r="B44" s="29" t="s">
         <v>139</v>
       </c>
@@ -8613,8 +8610,8 @@
       <c r="BE44" s="116"/>
       <c r="BF44" s="116"/>
     </row>
-    <row r="45" spans="1:58" ht="98.4" customHeight="1">
-      <c r="A45" s="227"/>
+    <row r="45" spans="1:58" ht="98.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="222"/>
       <c r="B45" s="29" t="s">
         <v>142</v>
       </c>
@@ -8756,8 +8753,8 @@
       <c r="BE45" s="116"/>
       <c r="BF45" s="116"/>
     </row>
-    <row r="46" spans="1:58" ht="67.95" customHeight="1">
-      <c r="A46" s="227"/>
+    <row r="46" spans="1:58" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="222"/>
       <c r="B46" s="29" t="s">
         <v>145</v>
       </c>
@@ -8900,8 +8897,8 @@
       <c r="BE46" s="116"/>
       <c r="BF46" s="116"/>
     </row>
-    <row r="47" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A47" s="226" t="s">
+    <row r="47" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="229" t="s">
         <v>148</v>
       </c>
       <c r="B47" s="29" t="s">
@@ -9009,8 +9006,8 @@
       <c r="BE47" s="116"/>
       <c r="BF47" s="116"/>
     </row>
-    <row r="48" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A48" s="226"/>
+    <row r="48" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="229"/>
       <c r="B48" s="29" t="s">
         <v>151</v>
       </c>
@@ -9127,8 +9124,8 @@
       <c r="BE48" s="116"/>
       <c r="BF48" s="116"/>
     </row>
-    <row r="49" spans="1:58" ht="51" customHeight="1">
-      <c r="A49" s="226"/>
+    <row r="49" spans="1:58" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="229"/>
       <c r="B49" s="29" t="s">
         <v>153</v>
       </c>
@@ -9243,8 +9240,8 @@
       <c r="BE49" s="116"/>
       <c r="BF49" s="116"/>
     </row>
-    <row r="50" spans="1:58" ht="51.6" customHeight="1">
-      <c r="A50" s="226"/>
+    <row r="50" spans="1:58" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="229"/>
       <c r="B50" s="29" t="s">
         <v>156</v>
       </c>
@@ -9348,8 +9345,8 @@
       <c r="BE50" s="116"/>
       <c r="BF50" s="116"/>
     </row>
-    <row r="51" spans="1:58" ht="40.950000000000003" customHeight="1">
-      <c r="A51" s="235"/>
+    <row r="51" spans="1:58" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="266"/>
       <c r="B51" s="30" t="s">
         <v>159</v>
       </c>
@@ -9453,11 +9450,11 @@
       <c r="BE51" s="116"/>
       <c r="BF51" s="116"/>
     </row>
-    <row r="52" spans="1:58" ht="13.2" customHeight="1">
-      <c r="A52" s="228" t="s">
+    <row r="52" spans="1:58" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="242" t="s">
         <v>162</v>
       </c>
-      <c r="B52" s="229"/>
+      <c r="B52" s="243"/>
       <c r="C52" s="92"/>
       <c r="D52" s="5" t="s">
         <v>17</v>
@@ -9523,8 +9520,8 @@
       <c r="BE52" s="116"/>
       <c r="BF52" s="116"/>
     </row>
-    <row r="53" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A53" s="225" t="s">
+    <row r="53" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="241" t="s">
         <v>163</v>
       </c>
       <c r="B53" s="86" t="s">
@@ -9619,8 +9616,8 @@
       <c r="BE53" s="116"/>
       <c r="BF53" s="116"/>
     </row>
-    <row r="54" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A54" s="231"/>
+    <row r="54" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="235"/>
       <c r="B54" s="29" t="s">
         <v>167</v>
       </c>
@@ -9713,8 +9710,8 @@
       <c r="BE54" s="116"/>
       <c r="BF54" s="116"/>
     </row>
-    <row r="55" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A55" s="222" t="s">
+    <row r="55" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="234" t="s">
         <v>170</v>
       </c>
       <c r="B55" s="43" t="s">
@@ -9809,8 +9806,8 @@
       <c r="BE55" s="116"/>
       <c r="BF55" s="116"/>
     </row>
-    <row r="56" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A56" s="222"/>
+    <row r="56" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="234"/>
       <c r="B56" s="29" t="s">
         <v>174</v>
       </c>
@@ -9924,8 +9921,8 @@
       <c r="BE56" s="116"/>
       <c r="BF56" s="116"/>
     </row>
-    <row r="57" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A57" s="222"/>
+    <row r="57" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="234"/>
       <c r="B57" s="29" t="s">
         <v>177</v>
       </c>
@@ -10018,8 +10015,8 @@
       <c r="BE57" s="116"/>
       <c r="BF57" s="116"/>
     </row>
-    <row r="58" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A58" s="222"/>
+    <row r="58" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="234"/>
       <c r="B58" s="29" t="s">
         <v>180</v>
       </c>
@@ -10112,7 +10109,7 @@
       <c r="BE58" s="116"/>
       <c r="BF58" s="116"/>
     </row>
-    <row r="59" spans="1:58" ht="60" customHeight="1">
+    <row r="59" spans="1:58" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="74" t="s">
         <v>183</v>
       </c>
@@ -10183,7 +10180,7 @@
       <c r="AG59" s="36"/>
       <c r="AH59" s="36"/>
       <c r="AI59" s="36"/>
-      <c r="AJ59" s="267">
+      <c r="AJ59" s="36">
         <v>2</v>
       </c>
       <c r="AK59" s="188">
@@ -10223,8 +10220,8 @@
       <c r="BE59" s="116"/>
       <c r="BF59" s="116"/>
     </row>
-    <row r="60" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A60" s="222" t="s">
+    <row r="60" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="234" t="s">
         <v>187</v>
       </c>
       <c r="B60" s="29" t="s">
@@ -10342,8 +10339,8 @@
       <c r="BE60" s="116"/>
       <c r="BF60" s="116"/>
     </row>
-    <row r="61" spans="1:58" ht="70.95" customHeight="1">
-      <c r="A61" s="231"/>
+    <row r="61" spans="1:58" ht="70.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="235"/>
       <c r="B61" s="29" t="s">
         <v>191</v>
       </c>
@@ -10460,8 +10457,8 @@
       <c r="BE61" s="116"/>
       <c r="BF61" s="116"/>
     </row>
-    <row r="62" spans="1:58" ht="33.6" customHeight="1">
-      <c r="A62" s="223"/>
+    <row r="62" spans="1:58" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="261"/>
       <c r="B62" s="30" t="s">
         <v>194</v>
       </c>
@@ -10583,11 +10580,11 @@
       <c r="BE62" s="116"/>
       <c r="BF62" s="116"/>
     </row>
-    <row r="63" spans="1:58" ht="13.2" customHeight="1">
-      <c r="A63" s="228" t="s">
+    <row r="63" spans="1:58" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="242" t="s">
         <v>197</v>
       </c>
-      <c r="B63" s="229"/>
+      <c r="B63" s="243"/>
       <c r="C63" s="92"/>
       <c r="D63" s="5" t="s">
         <v>17</v>
@@ -10653,8 +10650,8 @@
       <c r="BE63" s="116"/>
       <c r="BF63" s="116"/>
     </row>
-    <row r="64" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A64" s="225" t="s">
+    <row r="64" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="241" t="s">
         <v>198</v>
       </c>
       <c r="B64" s="86" t="s">
@@ -10753,8 +10750,8 @@
       <c r="BE64" s="116"/>
       <c r="BF64" s="116"/>
     </row>
-    <row r="65" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A65" s="231"/>
+    <row r="65" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="235"/>
       <c r="B65" s="29" t="s">
         <v>202</v>
       </c>
@@ -10849,7 +10846,7 @@
       <c r="BE65" s="116"/>
       <c r="BF65" s="116"/>
     </row>
-    <row r="66" spans="1:58" ht="43.5" customHeight="1">
+    <row r="66" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="29" t="s">
         <v>205</v>
       </c>
@@ -10945,7 +10942,7 @@
       <c r="BE66" s="116"/>
       <c r="BF66" s="116"/>
     </row>
-    <row r="67" spans="1:58" ht="78.599999999999994" customHeight="1">
+    <row r="67" spans="1:58" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="126" t="s">
         <v>209</v>
       </c>
@@ -11072,7 +11069,7 @@
       <c r="BE67" s="116"/>
       <c r="BF67" s="116"/>
     </row>
-    <row r="68" spans="1:58" ht="84">
+    <row r="68" spans="1:58" ht="84" x14ac:dyDescent="0.3">
       <c r="A68" s="126" t="s">
         <v>213</v>
       </c>
@@ -11193,7 +11190,7 @@
       <c r="BE68" s="116"/>
       <c r="BF68" s="116"/>
     </row>
-    <row r="69" spans="1:58" ht="69.75" customHeight="1">
+    <row r="69" spans="1:58" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="126" t="s">
         <v>217</v>
       </c>
@@ -11293,7 +11290,7 @@
       <c r="BE69" s="116"/>
       <c r="BF69" s="116"/>
     </row>
-    <row r="70" spans="1:58" ht="103.2" customHeight="1">
+    <row r="70" spans="1:58" ht="103.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="74" t="s">
         <v>221</v>
       </c>
@@ -11421,7 +11418,7 @@
       <c r="BE70" s="116"/>
       <c r="BF70" s="116"/>
     </row>
-    <row r="71" spans="1:58" ht="88.95" customHeight="1">
+    <row r="71" spans="1:58" ht="88.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="74" t="s">
         <v>225</v>
       </c>
@@ -11560,8 +11557,8 @@
       <c r="BE71" s="116"/>
       <c r="BF71" s="116"/>
     </row>
-    <row r="72" spans="1:58" ht="52.2" customHeight="1">
-      <c r="A72" s="227" t="s">
+    <row r="72" spans="1:58" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="222" t="s">
         <v>229</v>
       </c>
       <c r="B72" s="80" t="s">
@@ -11656,8 +11653,8 @@
       <c r="BE72" s="116"/>
       <c r="BF72" s="116"/>
     </row>
-    <row r="73" spans="1:58" ht="63" customHeight="1">
-      <c r="A73" s="227"/>
+    <row r="73" spans="1:58" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="222"/>
       <c r="B73" s="80" t="s">
         <v>233</v>
       </c>
@@ -11765,7 +11762,7 @@
       <c r="BE73" s="116"/>
       <c r="BF73" s="116"/>
     </row>
-    <row r="74" spans="1:58" ht="53.4" customHeight="1">
+    <row r="74" spans="1:58" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="74" t="s">
         <v>236</v>
       </c>
@@ -11867,8 +11864,8 @@
       <c r="BE74" s="116"/>
       <c r="BF74" s="116"/>
     </row>
-    <row r="75" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A75" s="227" t="s">
+    <row r="75" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="222" t="s">
         <v>240</v>
       </c>
       <c r="B75" s="29" t="s">
@@ -11971,8 +11968,8 @@
       <c r="BE75" s="116"/>
       <c r="BF75" s="116"/>
     </row>
-    <row r="76" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A76" s="226"/>
+    <row r="76" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="229"/>
       <c r="B76" s="29" t="s">
         <v>244</v>
       </c>
@@ -12075,8 +12072,8 @@
       <c r="BE76" s="116"/>
       <c r="BF76" s="116"/>
     </row>
-    <row r="77" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A77" s="226"/>
+    <row r="77" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="229"/>
       <c r="B77" s="29" t="s">
         <v>247</v>
       </c>
@@ -12179,8 +12176,8 @@
       <c r="BE77" s="116"/>
       <c r="BF77" s="116"/>
     </row>
-    <row r="78" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A78" s="226"/>
+    <row r="78" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="229"/>
       <c r="B78" s="29" t="s">
         <v>250</v>
       </c>
@@ -12283,8 +12280,8 @@
       <c r="BE78" s="116"/>
       <c r="BF78" s="116"/>
     </row>
-    <row r="79" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A79" s="226"/>
+    <row r="79" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="229"/>
       <c r="B79" s="29" t="s">
         <v>253</v>
       </c>
@@ -12387,8 +12384,8 @@
       <c r="BE79" s="116"/>
       <c r="BF79" s="116"/>
     </row>
-    <row r="80" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A80" s="226"/>
+    <row r="80" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="229"/>
       <c r="B80" s="29" t="s">
         <v>256</v>
       </c>
@@ -12491,8 +12488,8 @@
       <c r="BE80" s="116"/>
       <c r="BF80" s="116"/>
     </row>
-    <row r="81" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A81" s="226"/>
+    <row r="81" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="229"/>
       <c r="B81" s="29" t="s">
         <v>259</v>
       </c>
@@ -12595,8 +12592,8 @@
       <c r="BE81" s="116"/>
       <c r="BF81" s="116"/>
     </row>
-    <row r="82" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A82" s="227" t="s">
+    <row r="82" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="222" t="s">
         <v>262</v>
       </c>
       <c r="B82" s="29" t="s">
@@ -12705,8 +12702,8 @@
       <c r="BE82" s="116"/>
       <c r="BF82" s="116"/>
     </row>
-    <row r="83" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A83" s="227"/>
+    <row r="83" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="222"/>
       <c r="B83" s="29" t="s">
         <v>266</v>
       </c>
@@ -12812,8 +12809,8 @@
       <c r="BE83" s="116"/>
       <c r="BF83" s="116"/>
     </row>
-    <row r="84" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A84" s="227" t="s">
+    <row r="84" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="222" t="s">
         <v>269</v>
       </c>
       <c r="B84" s="29" t="s">
@@ -12916,8 +12913,8 @@
       <c r="BE84" s="116"/>
       <c r="BF84" s="116"/>
     </row>
-    <row r="85" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A85" s="227"/>
+    <row r="85" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="222"/>
       <c r="B85" s="29" t="s">
         <v>273</v>
       </c>
@@ -13018,8 +13015,8 @@
       <c r="BE85" s="116"/>
       <c r="BF85" s="116"/>
     </row>
-    <row r="86" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A86" s="227"/>
+    <row r="86" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="222"/>
       <c r="B86" s="29" t="s">
         <v>276</v>
       </c>
@@ -13120,8 +13117,8 @@
       <c r="BE86" s="116"/>
       <c r="BF86" s="116"/>
     </row>
-    <row r="87" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A87" s="227"/>
+    <row r="87" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="222"/>
       <c r="B87" s="29" t="s">
         <v>279</v>
       </c>
@@ -13222,8 +13219,8 @@
       <c r="BE87" s="116"/>
       <c r="BF87" s="116"/>
     </row>
-    <row r="88" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A88" s="227"/>
+    <row r="88" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="222"/>
       <c r="B88" s="29" t="s">
         <v>282</v>
       </c>
@@ -13324,8 +13321,8 @@
       <c r="BE88" s="116"/>
       <c r="BF88" s="116"/>
     </row>
-    <row r="89" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A89" s="227"/>
+    <row r="89" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="222"/>
       <c r="B89" s="50" t="s">
         <v>285</v>
       </c>
@@ -13426,8 +13423,8 @@
       <c r="BE89" s="116"/>
       <c r="BF89" s="116"/>
     </row>
-    <row r="90" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A90" s="227" t="s">
+    <row r="90" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="222" t="s">
         <v>288</v>
       </c>
       <c r="B90" s="29" t="s">
@@ -13531,8 +13528,8 @@
       <c r="BE90" s="116"/>
       <c r="BF90" s="116"/>
     </row>
-    <row r="91" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A91" s="227"/>
+    <row r="91" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="222"/>
       <c r="B91" s="29" t="s">
         <v>292</v>
       </c>
@@ -13634,8 +13631,8 @@
       <c r="BE91" s="116"/>
       <c r="BF91" s="116"/>
     </row>
-    <row r="92" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A92" s="227"/>
+    <row r="92" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="222"/>
       <c r="B92" s="29" t="s">
         <v>295</v>
       </c>
@@ -13737,8 +13734,8 @@
       <c r="BE92" s="116"/>
       <c r="BF92" s="116"/>
     </row>
-    <row r="93" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A93" s="227"/>
+    <row r="93" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="222"/>
       <c r="B93" s="29" t="s">
         <v>298</v>
       </c>
@@ -13845,8 +13842,8 @@
       <c r="BE93" s="116"/>
       <c r="BF93" s="116"/>
     </row>
-    <row r="94" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A94" s="227"/>
+    <row r="94" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="222"/>
       <c r="B94" s="29" t="s">
         <v>301</v>
       </c>
@@ -13955,8 +13952,8 @@
       <c r="BE94" s="116"/>
       <c r="BF94" s="116"/>
     </row>
-    <row r="95" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A95" s="227"/>
+    <row r="95" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="222"/>
       <c r="B95" s="29" t="s">
         <v>304</v>
       </c>
@@ -14065,8 +14062,8 @@
       <c r="BE95" s="116"/>
       <c r="BF95" s="116"/>
     </row>
-    <row r="96" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A96" s="226" t="s">
+    <row r="96" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="229" t="s">
         <v>307</v>
       </c>
       <c r="B96" s="29" t="s">
@@ -14161,8 +14158,8 @@
       <c r="BE96" s="116"/>
       <c r="BF96" s="116"/>
     </row>
-    <row r="97" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A97" s="226"/>
+    <row r="97" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="229"/>
       <c r="B97" s="29" t="s">
         <v>311</v>
       </c>
@@ -14263,8 +14260,8 @@
       <c r="BE97" s="116"/>
       <c r="BF97" s="116"/>
     </row>
-    <row r="98" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A98" s="226"/>
+    <row r="98" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="229"/>
       <c r="B98" s="29" t="s">
         <v>314</v>
       </c>
@@ -14357,7 +14354,7 @@
       <c r="BE98" s="116"/>
       <c r="BF98" s="116"/>
     </row>
-    <row r="99" spans="1:58" ht="43.5" customHeight="1">
+    <row r="99" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="112" t="s">
         <v>317</v>
       </c>
@@ -14464,7 +14461,7 @@
       <c r="BE99" s="116"/>
       <c r="BF99" s="116"/>
     </row>
-    <row r="100" spans="1:58" ht="64.95" customHeight="1">
+    <row r="100" spans="1:58" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="112" t="s">
         <v>321</v>
       </c>
@@ -14521,7 +14518,7 @@
       </c>
       <c r="AB100" s="36"/>
       <c r="AC100" s="36">
-        <f t="shared" ref="AC99:AC104" si="69">S100+I100</f>
+        <f t="shared" ref="AC100:AC104" si="69">S100+I100</f>
         <v>3</v>
       </c>
       <c r="AD100" s="36"/>
@@ -14531,7 +14528,7 @@
       </c>
       <c r="AG100" s="36"/>
       <c r="AH100" s="36">
-        <f t="shared" ref="AH99:AH104" si="70">X100+N100</f>
+        <f t="shared" ref="AH100:AH104" si="70">X100+N100</f>
         <v>2</v>
       </c>
       <c r="AI100" s="36"/>
@@ -14570,7 +14567,7 @@
       <c r="BE100" s="116"/>
       <c r="BF100" s="116"/>
     </row>
-    <row r="101" spans="1:58" ht="70.95" customHeight="1">
+    <row r="101" spans="1:58" ht="70.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="112" t="s">
         <v>325</v>
       </c>
@@ -14676,7 +14673,7 @@
       <c r="BE101" s="116"/>
       <c r="BF101" s="116"/>
     </row>
-    <row r="102" spans="1:58" ht="91.2" customHeight="1">
+    <row r="102" spans="1:58" ht="91.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="127" t="s">
         <v>329</v>
       </c>
@@ -14785,7 +14782,7 @@
       <c r="BE102" s="116"/>
       <c r="BF102" s="116"/>
     </row>
-    <row r="103" spans="1:58" ht="84">
+    <row r="103" spans="1:58" ht="84" x14ac:dyDescent="0.3">
       <c r="A103" s="112" t="s">
         <v>333</v>
       </c>
@@ -14896,7 +14893,7 @@
       <c r="BE103" s="116"/>
       <c r="BF103" s="116"/>
     </row>
-    <row r="104" spans="1:58" ht="43.5" customHeight="1">
+    <row r="104" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="125" t="s">
         <v>337</v>
       </c>
@@ -15008,11 +15005,11 @@
       <c r="BE104" s="116"/>
       <c r="BF104" s="116"/>
     </row>
-    <row r="105" spans="1:58" ht="15.45" customHeight="1">
-      <c r="A105" s="228" t="s">
+    <row r="105" spans="1:58" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="242" t="s">
         <v>341</v>
       </c>
-      <c r="B105" s="229"/>
+      <c r="B105" s="243"/>
       <c r="C105" s="92"/>
       <c r="D105" s="5" t="s">
         <v>17</v>
@@ -15078,8 +15075,8 @@
       <c r="BE105" s="116"/>
       <c r="BF105" s="116"/>
     </row>
-    <row r="106" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A106" s="230" t="s">
+    <row r="106" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="260" t="s">
         <v>342</v>
       </c>
       <c r="B106" s="86" t="s">
@@ -15190,8 +15187,8 @@
       <c r="BE106" s="116"/>
       <c r="BF106" s="116"/>
     </row>
-    <row r="107" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A107" s="226"/>
+    <row r="107" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="229"/>
       <c r="B107" s="29" t="s">
         <v>346</v>
       </c>
@@ -15300,8 +15297,8 @@
       <c r="BE107" s="116"/>
       <c r="BF107" s="116"/>
     </row>
-    <row r="108" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A108" s="226"/>
+    <row r="108" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="229"/>
       <c r="B108" s="29" t="s">
         <v>349</v>
       </c>
@@ -15410,8 +15407,8 @@
       <c r="BE108" s="116"/>
       <c r="BF108" s="116"/>
     </row>
-    <row r="109" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A109" s="226"/>
+    <row r="109" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="229"/>
       <c r="B109" s="29" t="s">
         <v>352</v>
       </c>
@@ -15520,8 +15517,8 @@
       <c r="BE109" s="116"/>
       <c r="BF109" s="116"/>
     </row>
-    <row r="110" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A110" s="226"/>
+    <row r="110" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="229"/>
       <c r="B110" s="29" t="s">
         <v>355</v>
       </c>
@@ -15630,8 +15627,8 @@
       <c r="BE110" s="116"/>
       <c r="BF110" s="116"/>
     </row>
-    <row r="111" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A111" s="227" t="s">
+    <row r="111" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="222" t="s">
         <v>358</v>
       </c>
       <c r="B111" s="29" t="s">
@@ -15740,8 +15737,8 @@
       <c r="BE111" s="116"/>
       <c r="BF111" s="116"/>
     </row>
-    <row r="112" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A112" s="227"/>
+    <row r="112" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="222"/>
       <c r="B112" s="52" t="s">
         <v>362</v>
       </c>
@@ -15848,8 +15845,8 @@
       <c r="BE112" s="116"/>
       <c r="BF112" s="116"/>
     </row>
-    <row r="113" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A113" s="226" t="s">
+    <row r="113" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="229" t="s">
         <v>365</v>
       </c>
       <c r="B113" s="29" t="s">
@@ -15957,8 +15954,8 @@
       <c r="BE113" s="116"/>
       <c r="BF113" s="116"/>
     </row>
-    <row r="114" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A114" s="226"/>
+    <row r="114" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="229"/>
       <c r="B114" s="29" t="s">
         <v>369</v>
       </c>
@@ -16065,8 +16062,8 @@
       <c r="BE114" s="116"/>
       <c r="BF114" s="116"/>
     </row>
-    <row r="115" spans="1:58" ht="82.95" customHeight="1">
-      <c r="A115" s="227" t="s">
+    <row r="115" spans="1:58" ht="82.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="222" t="s">
         <v>372</v>
       </c>
       <c r="B115" s="29" t="s">
@@ -16176,8 +16173,8 @@
       <c r="BE115" s="116"/>
       <c r="BF115" s="116"/>
     </row>
-    <row r="116" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A116" s="227"/>
+    <row r="116" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="222"/>
       <c r="B116" s="29" t="s">
         <v>376</v>
       </c>
@@ -16285,8 +16282,8 @@
       <c r="BE116" s="116"/>
       <c r="BF116" s="116"/>
     </row>
-    <row r="117" spans="1:58" ht="76.2" customHeight="1">
-      <c r="A117" s="227" t="s">
+    <row r="117" spans="1:58" ht="76.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="222" t="s">
         <v>379</v>
       </c>
       <c r="B117" s="39" t="s">
@@ -16396,8 +16393,8 @@
       <c r="BE117" s="116"/>
       <c r="BF117" s="116"/>
     </row>
-    <row r="118" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A118" s="226"/>
+    <row r="118" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="229"/>
       <c r="B118" s="39" t="s">
         <v>383</v>
       </c>
@@ -16505,8 +16502,8 @@
       <c r="BE118" s="116"/>
       <c r="BF118" s="116"/>
     </row>
-    <row r="119" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A119" s="223" t="s">
+    <row r="119" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="261" t="s">
         <v>385</v>
       </c>
       <c r="B119" s="37" t="s">
@@ -16607,8 +16604,8 @@
       <c r="BE119" s="116"/>
       <c r="BF119" s="116"/>
     </row>
-    <row r="120" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A120" s="224"/>
+    <row r="120" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="262"/>
       <c r="B120" s="37" t="s">
         <v>389</v>
       </c>
@@ -16707,8 +16704,8 @@
       <c r="BE120" s="116"/>
       <c r="BF120" s="116"/>
     </row>
-    <row r="121" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A121" s="225"/>
+    <row r="121" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="241"/>
       <c r="B121" s="37" t="s">
         <v>392</v>
       </c>
@@ -16807,8 +16804,8 @@
       <c r="BE121" s="116"/>
       <c r="BF121" s="116"/>
     </row>
-    <row r="122" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A122" s="226" t="s">
+    <row r="122" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="229" t="s">
         <v>395</v>
       </c>
       <c r="B122" s="29" t="s">
@@ -16922,8 +16919,8 @@
       <c r="BE122" s="116"/>
       <c r="BF122" s="116"/>
     </row>
-    <row r="123" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A123" s="226"/>
+    <row r="123" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="229"/>
       <c r="B123" s="29" t="s">
         <v>399</v>
       </c>
@@ -17035,8 +17032,8 @@
       <c r="BE123" s="116"/>
       <c r="BF123" s="116"/>
     </row>
-    <row r="124" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A124" s="226" t="s">
+    <row r="124" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="229" t="s">
         <v>401</v>
       </c>
       <c r="B124" s="29" t="s">
@@ -17095,23 +17092,21 @@
       <c r="AC124" s="36"/>
       <c r="AD124" s="36"/>
       <c r="AE124" s="36">
-        <f t="shared" si="85"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF124" s="32">
         <f t="shared" si="77"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG124" s="36"/>
       <c r="AH124" s="36"/>
       <c r="AI124" s="36"/>
       <c r="AJ124" s="36">
-        <f t="shared" si="86"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK124" s="188">
         <f>SUM(AG124:AJ124)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL124" s="168">
         <v>1</v>
@@ -17143,8 +17138,8 @@
       <c r="BE124" s="116"/>
       <c r="BF124" s="116"/>
     </row>
-    <row r="125" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A125" s="226"/>
+    <row r="125" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="229"/>
       <c r="B125" s="29" t="s">
         <v>405</v>
       </c>
@@ -17252,7 +17247,7 @@
       <c r="BE125" s="116"/>
       <c r="BF125" s="116"/>
     </row>
-    <row r="126" spans="1:58" ht="77.400000000000006" customHeight="1">
+    <row r="126" spans="1:58" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="29" t="s">
         <v>408</v>
       </c>
@@ -17381,8 +17376,8 @@
       <c r="BE126" s="116"/>
       <c r="BF126" s="116"/>
     </row>
-    <row r="127" spans="1:58" ht="99.6" customHeight="1">
-      <c r="A127" s="227" t="s">
+    <row r="127" spans="1:58" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="222" t="s">
         <v>412</v>
       </c>
       <c r="B127" s="29" t="s">
@@ -17495,8 +17490,8 @@
       <c r="BE127" s="116"/>
       <c r="BF127" s="116"/>
     </row>
-    <row r="128" spans="1:58" ht="98.4" customHeight="1">
-      <c r="A128" s="226"/>
+    <row r="128" spans="1:58" ht="98.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="229"/>
       <c r="B128" s="29" t="s">
         <v>416</v>
       </c>
@@ -17606,7 +17601,7 @@
       <c r="BE128" s="116"/>
       <c r="BF128" s="116"/>
     </row>
-    <row r="129" spans="1:58" ht="43.5" customHeight="1">
+    <row r="129" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="74" t="s">
         <v>419</v>
       </c>
@@ -17712,8 +17707,8 @@
       <c r="BE129" s="116"/>
       <c r="BF129" s="116"/>
     </row>
-    <row r="130" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A130" s="226" t="s">
+    <row r="130" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="229" t="s">
         <v>423</v>
       </c>
       <c r="B130" s="39" t="s">
@@ -17829,8 +17824,8 @@
       <c r="BE130" s="116"/>
       <c r="BF130" s="116"/>
     </row>
-    <row r="131" spans="1:58" ht="67.95" customHeight="1">
-      <c r="A131" s="226"/>
+    <row r="131" spans="1:58" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="229"/>
       <c r="B131" s="39" t="s">
         <v>427</v>
       </c>
@@ -17944,8 +17939,8 @@
       <c r="BE131" s="116"/>
       <c r="BF131" s="116"/>
     </row>
-    <row r="132" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A132" s="227" t="s">
+    <row r="132" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="222" t="s">
         <v>430</v>
       </c>
       <c r="B132" s="29" t="s">
@@ -18038,8 +18033,8 @@
       <c r="BE132" s="116"/>
       <c r="BF132" s="116"/>
     </row>
-    <row r="133" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A133" s="227"/>
+    <row r="133" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="222"/>
       <c r="B133" s="29" t="s">
         <v>434</v>
       </c>
@@ -18130,8 +18125,8 @@
       <c r="BE133" s="116"/>
       <c r="BF133" s="116"/>
     </row>
-    <row r="134" spans="1:58" ht="53.4" customHeight="1">
-      <c r="A134" s="222" t="s">
+    <row r="134" spans="1:58" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="234" t="s">
         <v>437</v>
       </c>
       <c r="B134" s="39" t="s">
@@ -18234,8 +18229,8 @@
       <c r="BE134" s="116"/>
       <c r="BF134" s="116"/>
     </row>
-    <row r="135" spans="1:58" ht="43.5" customHeight="1">
-      <c r="A135" s="222"/>
+    <row r="135" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="234"/>
       <c r="B135" s="39" t="s">
         <v>441</v>
       </c>
@@ -18336,7 +18331,7 @@
       <c r="BE135" s="116"/>
       <c r="BF135" s="116"/>
     </row>
-    <row r="136" spans="1:58" ht="16.2" customHeight="1">
+    <row r="136" spans="1:58" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="111" t="s">
         <v>444</v>
       </c>
@@ -18406,7 +18401,7 @@
       <c r="BE136" s="116"/>
       <c r="BF136" s="116"/>
     </row>
-    <row r="137" spans="1:58" ht="43.5" customHeight="1">
+    <row r="137" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="104" t="s">
         <v>445</v>
       </c>
@@ -18519,7 +18514,7 @@
       <c r="BE137" s="116"/>
       <c r="BF137" s="116"/>
     </row>
-    <row r="138" spans="1:58" ht="43.5" customHeight="1">
+    <row r="138" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="39" t="s">
         <v>449</v>
       </c>
@@ -18632,7 +18627,7 @@
       <c r="BE138" s="116"/>
       <c r="BF138" s="116"/>
     </row>
-    <row r="139" spans="1:58" ht="43.5" customHeight="1">
+    <row r="139" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="39" t="s">
         <v>453</v>
       </c>
@@ -18745,7 +18740,7 @@
       <c r="BE139" s="116"/>
       <c r="BF139" s="116"/>
     </row>
-    <row r="140" spans="1:58" ht="43.5" customHeight="1">
+    <row r="140" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="39" t="s">
         <v>457</v>
       </c>
@@ -18856,7 +18851,7 @@
       <c r="BE140" s="116"/>
       <c r="BF140" s="116"/>
     </row>
-    <row r="141" spans="1:58" ht="43.5" customHeight="1" thickBot="1">
+    <row r="141" spans="1:58" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="39" t="s">
         <v>461</v>
       </c>
@@ -18969,7 +18964,7 @@
       <c r="BE141" s="116"/>
       <c r="BF141" s="116"/>
     </row>
-    <row r="142" spans="1:58" ht="43.5" customHeight="1" thickBot="1">
+    <row r="142" spans="1:58" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="39" t="s">
         <v>465</v>
       </c>
@@ -19061,7 +19056,7 @@
       <c r="BE142" s="116"/>
       <c r="BF142" s="116"/>
     </row>
-    <row r="143" spans="1:58" ht="43.5" customHeight="1">
+    <row r="143" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="129"/>
       <c r="B143" s="116"/>
       <c r="C143" s="116"/>
@@ -19121,7 +19116,7 @@
       <c r="BE143" s="116"/>
       <c r="BF143" s="116"/>
     </row>
-    <row r="144" spans="1:58" ht="43.5" customHeight="1">
+    <row r="144" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="129"/>
       <c r="B144" s="116"/>
       <c r="C144" s="116"/>
@@ -19181,7 +19176,7 @@
       <c r="BE144" s="116"/>
       <c r="BF144" s="116"/>
     </row>
-    <row r="145" spans="1:58" ht="43.5" customHeight="1">
+    <row r="145" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="129"/>
       <c r="B145" s="116"/>
       <c r="C145" s="116"/>
@@ -19241,7 +19236,7 @@
       <c r="BE145" s="116"/>
       <c r="BF145" s="116"/>
     </row>
-    <row r="146" spans="1:58" ht="43.5" customHeight="1">
+    <row r="146" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="129"/>
       <c r="B146" s="116"/>
       <c r="C146" s="116"/>
@@ -19301,7 +19296,7 @@
       <c r="BE146" s="116"/>
       <c r="BF146" s="116"/>
     </row>
-    <row r="147" spans="1:58" ht="43.5" customHeight="1">
+    <row r="147" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="129"/>
       <c r="B147" s="116"/>
       <c r="C147" s="116"/>
@@ -19361,7 +19356,7 @@
       <c r="BE147" s="116"/>
       <c r="BF147" s="116"/>
     </row>
-    <row r="148" spans="1:58" ht="43.5" customHeight="1">
+    <row r="148" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="132"/>
       <c r="B148" s="116"/>
       <c r="C148" s="116"/>
@@ -19421,7 +19416,7 @@
       <c r="BE148" s="116"/>
       <c r="BF148" s="116"/>
     </row>
-    <row r="149" spans="1:58" ht="43.5" customHeight="1">
+    <row r="149" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="132"/>
       <c r="B149" s="116"/>
       <c r="C149" s="116"/>
@@ -19481,7 +19476,7 @@
       <c r="BE149" s="116"/>
       <c r="BF149" s="116"/>
     </row>
-    <row r="150" spans="1:58" ht="43.5" customHeight="1">
+    <row r="150" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="133"/>
       <c r="B150" s="116"/>
       <c r="C150" s="116"/>
@@ -19541,7 +19536,7 @@
       <c r="BE150" s="116"/>
       <c r="BF150" s="116"/>
     </row>
-    <row r="151" spans="1:58" ht="43.5" customHeight="1">
+    <row r="151" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="133"/>
       <c r="B151" s="116"/>
       <c r="C151" s="116"/>
@@ -19601,7 +19596,7 @@
       <c r="BE151" s="116"/>
       <c r="BF151" s="116"/>
     </row>
-    <row r="152" spans="1:58" ht="43.5" customHeight="1">
+    <row r="152" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="133"/>
       <c r="B152" s="116"/>
       <c r="C152" s="116"/>
@@ -19662,9 +19657,43 @@
       <c r="BF152" s="116"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="FvkE5EIW/Qigjaxb+oSXaiFky9kZWBQZ9jsJ613J+/AQIqbrmPoD8cmDynF3OyR7/7E4F4oFAGfVkDVrKDtlwA==" saltValue="KGDtBOASnZwiEYwBpmSShw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="MZNFbxzz2/HCMe/vUn4I7zMAcKMM2kHoG3KwocFq10m0xSTxu80AGOsAFxVjiYagbLKeGxjJfnWAPiknog8BQw==" saltValue="2hbpJChDnOW/peDO9z7CRw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <autoFilter ref="A8:BF142" xr:uid="{FF0FD833-DA25-49DC-8173-D7C8564C9878}"/>
   <mergeCells count="50">
+    <mergeCell ref="A60:A62"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="A42:A46"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="A119:A121"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A127:A128"/>
+    <mergeCell ref="A111:A112"/>
+    <mergeCell ref="A113:A114"/>
+    <mergeCell ref="A115:A116"/>
+    <mergeCell ref="A106:A110"/>
+    <mergeCell ref="A84:A89"/>
+    <mergeCell ref="A90:A95"/>
+    <mergeCell ref="A96:A98"/>
+    <mergeCell ref="A105:B105"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="H7:L7"/>
+    <mergeCell ref="M7:Q7"/>
+    <mergeCell ref="R7:V7"/>
+    <mergeCell ref="W7:AA7"/>
+    <mergeCell ref="H6:Q6"/>
+    <mergeCell ref="R6:AA6"/>
+    <mergeCell ref="AL6:AN7"/>
+    <mergeCell ref="AB6:AK6"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="AG7:AK7"/>
     <mergeCell ref="A82:A83"/>
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="D7:G7"/>
@@ -19681,40 +19710,6 @@
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="A63:B63"/>
     <mergeCell ref="A34:B34"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="H7:L7"/>
-    <mergeCell ref="M7:Q7"/>
-    <mergeCell ref="R7:V7"/>
-    <mergeCell ref="W7:AA7"/>
-    <mergeCell ref="H6:Q6"/>
-    <mergeCell ref="R6:AA6"/>
-    <mergeCell ref="AL6:AN7"/>
-    <mergeCell ref="AB6:AK6"/>
-    <mergeCell ref="AB7:AF7"/>
-    <mergeCell ref="AG7:AK7"/>
-    <mergeCell ref="A111:A112"/>
-    <mergeCell ref="A113:A114"/>
-    <mergeCell ref="A115:A116"/>
-    <mergeCell ref="A106:A110"/>
-    <mergeCell ref="A84:A89"/>
-    <mergeCell ref="A90:A95"/>
-    <mergeCell ref="A96:A98"/>
-    <mergeCell ref="A105:B105"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="A117:A118"/>
-    <mergeCell ref="A119:A121"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A127:A128"/>
-    <mergeCell ref="A60:A62"/>
-    <mergeCell ref="A37:A39"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="A42:A46"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A52:B52"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19740,6 +19735,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010032D42CB87088684C8C55529ACA400833" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="116a614d5496bbbd47bb867636028f47">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="059fd7f8-59e3-4ad4-b295-2c7569ffaa28" xmlns:ns3="e689b4b5-7069-4f87-a0fb-7ffa9fc42158" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2fda7db35d65f605230d67fc195a5aa9" ns2:_="" ns3:_="">
     <xsd:import namespace="059fd7f8-59e3-4ad4-b295-2c7569ffaa28"/>
@@ -19962,15 +19966,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4441BF8-F257-49EE-99C1-FF4F670D09C3}">
   <ds:schemaRefs>
@@ -19989,6 +19984,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A8ABC59-4B92-499E-809B-1276582C514D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5A2E045-8194-4DF4-AF94-5B802E4F288D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20005,12 +20008,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A8ABC59-4B92-499E-809B-1276582C514D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/assets/SCC_Log_Frame.xlsx
+++ b/assets/SCC_Log_Frame.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ZN108\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drcngo.sharepoint.com/sites/SYR-syrext-WS/01 Consortium/Syria Community Consortium/04 MEAL/13 IM/Navigator/Resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D85848-A7D6-48C4-A6BB-EEE28412A0C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{A3D85848-A7D6-48C4-A6BB-EEE28412A0C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40EB22C7-FE4C-43BA-A8AD-A64F21FC0DFD}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-870" windowWidth="29040" windowHeight="15720" tabRatio="885" xr2:uid="{00AD3E43-05CC-45FC-A0FF-E89A67A13665}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="885" xr2:uid="{00AD3E43-05CC-45FC-A0FF-E89A67A13665}"/>
   </bookViews>
   <sheets>
     <sheet name="2. LFA" sheetId="11" r:id="rId1"/>
@@ -769,16 +769,10 @@
     <t>Output 2.1.4.3</t>
   </si>
   <si>
-    <t>This indicator measures all participants graduating from business management training. Note that 2.1.4.3 and and 2.1.4.4 are independent and unique beneficiaries</t>
-  </si>
-  <si>
     <t># of Start-up participants graduated from technical trainings and business management training</t>
   </si>
   <si>
     <t>Output 2.1.4.4</t>
-  </si>
-  <si>
-    <t>These participants receive an additional training (technical/startup) because of being identified as needing this due to the specifics of their business. Note that 2.1.4.3 and and 2.1.4.4 are independent and unique beneficiaries</t>
   </si>
   <si>
     <t># of participants received business support (in-kind/cash)</t>
@@ -2203,6 +2197,15 @@
   <si>
     <t>Danish MoFA, SDC, Norwegian MoFA</t>
   </si>
+  <si>
+    <t>This indicator measures all participants graduating from business management training. 
+DRC, NRC: Note that 2.1.4.3 and and 2.1.4.4 are independent and unique beneficiaries.
+Oxfam: See context below in 2.1.4.4</t>
+  </si>
+  <si>
+    <t>DRC, NRC: These participants receive an additional training (technical/startup) because of being identified as needing this due to the specifics of their business. Note that 2.1.4.3 and and 2.1.4.4 are independent and unique beneficiaries.
+Oxfam: These are not unique beneficiaries to 2.1.4.3: they are taken from a subset of the 2.1.4.3 participants who will receive coaching. and a portion of these participants will receive business support through grants.</t>
+  </si>
 </sst>
 </file>
 
@@ -2213,7 +2216,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3754,9 +3757,96 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -3775,9 +3865,6 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3790,12 +3877,6 @@
     <xf numFmtId="0" fontId="21" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3809,84 +3890,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4274,7 +4277,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0FD833-DA25-49DC-8173-D7C8564C9878}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:BF152"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="43.5" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="43.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="128" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
@@ -4309,7 +4312,7 @@
     <col min="43" max="44" width="9.109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" ht="6.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:58" ht="6.6" hidden="1" customHeight="1">
       <c r="A1" s="122"/>
       <c r="B1" s="28"/>
       <c r="C1" s="76"/>
@@ -4369,7 +4372,7 @@
       <c r="BE1" s="116"/>
       <c r="BF1" s="116"/>
     </row>
-    <row r="2" spans="1:58" ht="21.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:58" ht="21.6" hidden="1" customHeight="1">
       <c r="A2" s="28"/>
       <c r="B2" s="28"/>
       <c r="C2" s="76"/>
@@ -4429,7 +4432,7 @@
       <c r="BE2" s="116"/>
       <c r="BF2" s="116"/>
     </row>
-    <row r="3" spans="1:58" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:58" ht="19.2" customHeight="1">
       <c r="A3" s="197" t="s">
         <v>2</v>
       </c>
@@ -4437,10 +4440,10 @@
         <v>45762</v>
       </c>
       <c r="C3" s="221" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D3" s="220" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E3" s="27"/>
       <c r="F3" s="27"/>
@@ -4497,7 +4500,7 @@
       <c r="BE3" s="116"/>
       <c r="BF3" s="116"/>
     </row>
-    <row r="4" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:58" ht="15" customHeight="1">
       <c r="A4" s="199" t="s">
         <v>3</v>
       </c>
@@ -4561,7 +4564,7 @@
       <c r="BE4" s="116"/>
       <c r="BF4" s="116"/>
     </row>
-    <row r="5" spans="1:58" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:58" ht="20.25" customHeight="1" thickBot="1">
       <c r="A5" s="200" t="s">
         <v>5</v>
       </c>
@@ -4625,60 +4628,60 @@
       <c r="BE5" s="116"/>
       <c r="BF5" s="116"/>
     </row>
-    <row r="6" spans="1:58" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="232" t="s">
+    <row r="6" spans="1:58" ht="24.6" customHeight="1">
+      <c r="A6" s="260" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="155"/>
       <c r="C6" s="154"/>
-      <c r="D6" s="223" t="s">
+      <c r="D6" s="252" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="224"/>
-      <c r="F6" s="224"/>
-      <c r="G6" s="225"/>
-      <c r="H6" s="250" t="s">
+      <c r="E6" s="253"/>
+      <c r="F6" s="253"/>
+      <c r="G6" s="254"/>
+      <c r="H6" s="242" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="251"/>
-      <c r="J6" s="251"/>
-      <c r="K6" s="251"/>
-      <c r="L6" s="251"/>
-      <c r="M6" s="251"/>
-      <c r="N6" s="251"/>
-      <c r="O6" s="251"/>
-      <c r="P6" s="251"/>
-      <c r="Q6" s="252"/>
-      <c r="R6" s="253" t="s">
+      <c r="I6" s="243"/>
+      <c r="J6" s="243"/>
+      <c r="K6" s="243"/>
+      <c r="L6" s="243"/>
+      <c r="M6" s="243"/>
+      <c r="N6" s="243"/>
+      <c r="O6" s="243"/>
+      <c r="P6" s="243"/>
+      <c r="Q6" s="244"/>
+      <c r="R6" s="245" t="s">
         <v>10</v>
       </c>
-      <c r="S6" s="253"/>
-      <c r="T6" s="253"/>
-      <c r="U6" s="253"/>
-      <c r="V6" s="253"/>
-      <c r="W6" s="253"/>
-      <c r="X6" s="253"/>
-      <c r="Y6" s="253"/>
-      <c r="Z6" s="253"/>
-      <c r="AA6" s="250"/>
-      <c r="AB6" s="253" t="s">
-        <v>469</v>
-      </c>
-      <c r="AC6" s="253"/>
-      <c r="AD6" s="253"/>
-      <c r="AE6" s="253"/>
-      <c r="AF6" s="253"/>
-      <c r="AG6" s="253"/>
-      <c r="AH6" s="253"/>
-      <c r="AI6" s="253"/>
-      <c r="AJ6" s="253"/>
-      <c r="AK6" s="250"/>
-      <c r="AL6" s="254" t="s">
+      <c r="S6" s="245"/>
+      <c r="T6" s="245"/>
+      <c r="U6" s="245"/>
+      <c r="V6" s="245"/>
+      <c r="W6" s="245"/>
+      <c r="X6" s="245"/>
+      <c r="Y6" s="245"/>
+      <c r="Z6" s="245"/>
+      <c r="AA6" s="242"/>
+      <c r="AB6" s="245" t="s">
+        <v>467</v>
+      </c>
+      <c r="AC6" s="245"/>
+      <c r="AD6" s="245"/>
+      <c r="AE6" s="245"/>
+      <c r="AF6" s="245"/>
+      <c r="AG6" s="245"/>
+      <c r="AH6" s="245"/>
+      <c r="AI6" s="245"/>
+      <c r="AJ6" s="245"/>
+      <c r="AK6" s="242"/>
+      <c r="AL6" s="246" t="s">
         <v>11</v>
       </c>
-      <c r="AM6" s="255"/>
-      <c r="AN6" s="256"/>
-      <c r="AO6" s="244" t="s">
+      <c r="AM6" s="247"/>
+      <c r="AN6" s="248"/>
+      <c r="AO6" s="236" t="s">
         <v>12</v>
       </c>
       <c r="AP6" s="114"/>
@@ -4699,66 +4702,66 @@
       <c r="BE6" s="116"/>
       <c r="BF6" s="116"/>
     </row>
-    <row r="7" spans="1:58" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="233"/>
+    <row r="7" spans="1:58" ht="16.2" customHeight="1">
+      <c r="A7" s="261"/>
       <c r="B7" s="153" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="226" t="s">
+      <c r="D7" s="255" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="227"/>
-      <c r="F7" s="227"/>
-      <c r="G7" s="228"/>
-      <c r="H7" s="246" t="s">
+      <c r="E7" s="256"/>
+      <c r="F7" s="256"/>
+      <c r="G7" s="257"/>
+      <c r="H7" s="238" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="247"/>
-      <c r="J7" s="247"/>
-      <c r="K7" s="247"/>
-      <c r="L7" s="248"/>
-      <c r="M7" s="246" t="s">
+      <c r="I7" s="239"/>
+      <c r="J7" s="239"/>
+      <c r="K7" s="239"/>
+      <c r="L7" s="240"/>
+      <c r="M7" s="238" t="s">
         <v>1</v>
       </c>
-      <c r="N7" s="247"/>
-      <c r="O7" s="247"/>
-      <c r="P7" s="247"/>
-      <c r="Q7" s="248"/>
-      <c r="R7" s="249" t="s">
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="239"/>
+      <c r="Q7" s="240"/>
+      <c r="R7" s="241" t="s">
         <v>16</v>
       </c>
-      <c r="S7" s="249"/>
-      <c r="T7" s="249"/>
-      <c r="U7" s="249"/>
-      <c r="V7" s="249"/>
-      <c r="W7" s="249" t="s">
+      <c r="S7" s="241"/>
+      <c r="T7" s="241"/>
+      <c r="U7" s="241"/>
+      <c r="V7" s="241"/>
+      <c r="W7" s="241" t="s">
         <v>1</v>
       </c>
-      <c r="X7" s="249"/>
-      <c r="Y7" s="249"/>
-      <c r="Z7" s="249"/>
-      <c r="AA7" s="246"/>
-      <c r="AB7" s="249" t="s">
+      <c r="X7" s="241"/>
+      <c r="Y7" s="241"/>
+      <c r="Z7" s="241"/>
+      <c r="AA7" s="238"/>
+      <c r="AB7" s="241" t="s">
         <v>16</v>
       </c>
-      <c r="AC7" s="249"/>
-      <c r="AD7" s="249"/>
-      <c r="AE7" s="249"/>
-      <c r="AF7" s="249"/>
-      <c r="AG7" s="249" t="s">
+      <c r="AC7" s="241"/>
+      <c r="AD7" s="241"/>
+      <c r="AE7" s="241"/>
+      <c r="AF7" s="241"/>
+      <c r="AG7" s="241" t="s">
         <v>1</v>
       </c>
-      <c r="AH7" s="249"/>
-      <c r="AI7" s="249"/>
-      <c r="AJ7" s="249"/>
-      <c r="AK7" s="246"/>
-      <c r="AL7" s="257"/>
-      <c r="AM7" s="258"/>
-      <c r="AN7" s="259"/>
-      <c r="AO7" s="245"/>
+      <c r="AH7" s="241"/>
+      <c r="AI7" s="241"/>
+      <c r="AJ7" s="241"/>
+      <c r="AK7" s="238"/>
+      <c r="AL7" s="249"/>
+      <c r="AM7" s="250"/>
+      <c r="AN7" s="251"/>
+      <c r="AO7" s="237"/>
       <c r="AP7" s="114"/>
       <c r="AQ7" s="114"/>
       <c r="AR7" s="114"/>
@@ -4777,8 +4780,8 @@
       <c r="BE7" s="116"/>
       <c r="BF7" s="116"/>
     </row>
-    <row r="8" spans="1:58" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="233"/>
+    <row r="8" spans="1:58" ht="21.6" customHeight="1" thickBot="1">
+      <c r="A8" s="261"/>
       <c r="B8" s="1"/>
       <c r="C8" s="2"/>
       <c r="D8" s="5" t="s">
@@ -4892,7 +4895,7 @@
       <c r="AN8" s="157" t="s">
         <v>21</v>
       </c>
-      <c r="AO8" s="245"/>
+      <c r="AO8" s="237"/>
       <c r="AP8" s="115"/>
       <c r="AQ8" s="115"/>
       <c r="AR8" s="115"/>
@@ -4911,8 +4914,8 @@
       <c r="BE8" s="116"/>
       <c r="BF8" s="116"/>
     </row>
-    <row r="9" spans="1:58" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="237" t="s">
+    <row r="9" spans="1:58" ht="36.75" customHeight="1" thickBot="1">
+      <c r="A9" s="263" t="s">
         <v>23</v>
       </c>
       <c r="B9" s="15" t="s">
@@ -5010,8 +5013,8 @@
       <c r="BE9" s="116"/>
       <c r="BF9" s="116"/>
     </row>
-    <row r="10" spans="1:58" ht="28.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="238"/>
+    <row r="10" spans="1:58" ht="28.95" customHeight="1" thickBot="1">
+      <c r="A10" s="264"/>
       <c r="B10" s="24" t="s">
         <v>27</v>
       </c>
@@ -5104,8 +5107,8 @@
       <c r="BE10" s="116"/>
       <c r="BF10" s="116"/>
     </row>
-    <row r="11" spans="1:58" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="239"/>
+    <row r="11" spans="1:58" ht="44.25" customHeight="1">
+      <c r="A11" s="265"/>
       <c r="B11" s="24" t="s">
         <v>30</v>
       </c>
@@ -5200,8 +5203,8 @@
       <c r="BE11" s="116"/>
       <c r="BF11" s="116"/>
     </row>
-    <row r="12" spans="1:58" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="240"/>
+    <row r="12" spans="1:58" ht="28.95" customHeight="1">
+      <c r="A12" s="266"/>
       <c r="B12" s="16" t="s">
         <v>33</v>
       </c>
@@ -5296,11 +5299,11 @@
       <c r="BE12" s="116"/>
       <c r="BF12" s="116"/>
     </row>
-    <row r="13" spans="1:58" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="230" t="s">
+    <row r="13" spans="1:58" ht="15.6" customHeight="1">
+      <c r="A13" s="258" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="231"/>
+      <c r="B13" s="259"/>
       <c r="C13" s="97"/>
       <c r="D13" s="5" t="s">
         <v>17</v>
@@ -5366,8 +5369,8 @@
       <c r="BE13" s="116"/>
       <c r="BF13" s="116"/>
     </row>
-    <row r="14" spans="1:58" ht="85.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="236" t="s">
+    <row r="14" spans="1:58" ht="85.2" customHeight="1">
+      <c r="A14" s="262" t="s">
         <v>37</v>
       </c>
       <c r="B14" s="86" t="s">
@@ -5464,8 +5467,8 @@
       <c r="BE14" s="116"/>
       <c r="BF14" s="116"/>
     </row>
-    <row r="15" spans="1:58" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="234"/>
+    <row r="15" spans="1:58" ht="51.75" customHeight="1">
+      <c r="A15" s="222"/>
       <c r="B15" s="29" t="s">
         <v>41</v>
       </c>
@@ -5560,8 +5563,8 @@
       <c r="BE15" s="116"/>
       <c r="BF15" s="116"/>
     </row>
-    <row r="16" spans="1:58" ht="36" x14ac:dyDescent="0.3">
-      <c r="A16" s="234"/>
+    <row r="16" spans="1:58" ht="36">
+      <c r="A16" s="222"/>
       <c r="B16" s="29" t="s">
         <v>44</v>
       </c>
@@ -5656,8 +5659,8 @@
       <c r="BE16" s="116"/>
       <c r="BF16" s="116"/>
     </row>
-    <row r="17" spans="1:58" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="234" t="s">
+    <row r="17" spans="1:58" ht="61.2" customHeight="1">
+      <c r="A17" s="222" t="s">
         <v>47</v>
       </c>
       <c r="B17" s="29" t="s">
@@ -5754,8 +5757,8 @@
       <c r="BE17" s="116"/>
       <c r="BF17" s="116"/>
     </row>
-    <row r="18" spans="1:58" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="234"/>
+    <row r="18" spans="1:58" ht="48.75" customHeight="1">
+      <c r="A18" s="222"/>
       <c r="B18" s="35" t="s">
         <v>51</v>
       </c>
@@ -5850,8 +5853,8 @@
       <c r="BE18" s="116"/>
       <c r="BF18" s="116"/>
     </row>
-    <row r="19" spans="1:58" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="234"/>
+    <row r="19" spans="1:58" ht="50.4" customHeight="1">
+      <c r="A19" s="222"/>
       <c r="B19" s="29" t="s">
         <v>54</v>
       </c>
@@ -5946,8 +5949,8 @@
       <c r="BE19" s="116"/>
       <c r="BF19" s="116"/>
     </row>
-    <row r="20" spans="1:58" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="234"/>
+    <row r="20" spans="1:58" ht="51.6" customHeight="1">
+      <c r="A20" s="222"/>
       <c r="B20" s="29" t="s">
         <v>57</v>
       </c>
@@ -6042,8 +6045,8 @@
       <c r="BE20" s="116"/>
       <c r="BF20" s="116"/>
     </row>
-    <row r="21" spans="1:58" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="234"/>
+    <row r="21" spans="1:58" ht="43.2" customHeight="1">
+      <c r="A21" s="222"/>
       <c r="B21" s="29" t="s">
         <v>60</v>
       </c>
@@ -6138,8 +6141,8 @@
       <c r="BE21" s="116"/>
       <c r="BF21" s="116"/>
     </row>
-    <row r="22" spans="1:58" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="234" t="s">
+    <row r="22" spans="1:58" ht="57" customHeight="1">
+      <c r="A22" s="222" t="s">
         <v>63</v>
       </c>
       <c r="B22" s="37" t="s">
@@ -6243,8 +6246,8 @@
       <c r="BE22" s="116"/>
       <c r="BF22" s="116"/>
     </row>
-    <row r="23" spans="1:58" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="235"/>
+    <row r="23" spans="1:58" ht="51" customHeight="1">
+      <c r="A23" s="223"/>
       <c r="B23" s="37" t="s">
         <v>67</v>
       </c>
@@ -6342,7 +6345,7 @@
       <c r="BE23" s="116"/>
       <c r="BF23" s="116"/>
     </row>
-    <row r="24" spans="1:58" ht="138.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:58" ht="138.6" customHeight="1">
       <c r="A24" s="29" t="s">
         <v>70</v>
       </c>
@@ -6447,7 +6450,7 @@
       <c r="BE24" s="116"/>
       <c r="BF24" s="116"/>
     </row>
-    <row r="25" spans="1:58" ht="98.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:58" ht="98.4" customHeight="1">
       <c r="A25" s="39" t="s">
         <v>74</v>
       </c>
@@ -6554,8 +6557,8 @@
       <c r="BE25" s="116"/>
       <c r="BF25" s="116"/>
     </row>
-    <row r="26" spans="1:58" ht="36" x14ac:dyDescent="0.3">
-      <c r="A26" s="229" t="s">
+    <row r="26" spans="1:58" ht="36">
+      <c r="A26" s="228" t="s">
         <v>78</v>
       </c>
       <c r="B26" s="29" t="s">
@@ -6667,8 +6670,8 @@
       <c r="BE26" s="116"/>
       <c r="BF26" s="116"/>
     </row>
-    <row r="27" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="229"/>
+    <row r="27" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A27" s="228"/>
       <c r="B27" s="29" t="s">
         <v>82</v>
       </c>
@@ -6778,8 +6781,8 @@
       <c r="BE27" s="116"/>
       <c r="BF27" s="116"/>
     </row>
-    <row r="28" spans="1:58" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="229"/>
+    <row r="28" spans="1:58" ht="44.4" customHeight="1">
+      <c r="A28" s="228"/>
       <c r="B28" s="29" t="s">
         <v>84</v>
       </c>
@@ -6891,8 +6894,8 @@
       <c r="BE28" s="116"/>
       <c r="BF28" s="116"/>
     </row>
-    <row r="29" spans="1:58" ht="58.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="229"/>
+    <row r="29" spans="1:58" ht="58.95" customHeight="1">
+      <c r="A29" s="228"/>
       <c r="B29" s="29" t="s">
         <v>87</v>
       </c>
@@ -7000,7 +7003,7 @@
       <c r="BE29" s="116"/>
       <c r="BF29" s="116"/>
     </row>
-    <row r="30" spans="1:58" ht="97.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:58" ht="97.2" customHeight="1">
       <c r="A30" s="74" t="s">
         <v>90</v>
       </c>
@@ -7107,7 +7110,7 @@
       <c r="BE30" s="116"/>
       <c r="BF30" s="116"/>
     </row>
-    <row r="31" spans="1:58" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:58" ht="84" customHeight="1">
       <c r="A31" s="112" t="s">
         <v>94</v>
       </c>
@@ -7222,7 +7225,7 @@
       <c r="BE31" s="116"/>
       <c r="BF31" s="116"/>
     </row>
-    <row r="32" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:58" ht="43.5" customHeight="1">
       <c r="A32" s="74" t="s">
         <v>97</v>
       </c>
@@ -7341,7 +7344,7 @@
       <c r="BE32" s="116"/>
       <c r="BF32" s="116"/>
     </row>
-    <row r="33" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:58" ht="43.5" customHeight="1">
       <c r="A33" s="123" t="s">
         <v>101</v>
       </c>
@@ -7444,11 +7447,11 @@
       <c r="BE33" s="116"/>
       <c r="BF33" s="116"/>
     </row>
-    <row r="34" spans="1:58" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="242" t="s">
+    <row r="34" spans="1:58" ht="12" customHeight="1">
+      <c r="A34" s="232" t="s">
         <v>106</v>
       </c>
-      <c r="B34" s="243"/>
+      <c r="B34" s="233"/>
       <c r="C34" s="92"/>
       <c r="D34" s="5" t="s">
         <v>17</v>
@@ -7514,8 +7517,8 @@
       <c r="BE34" s="116"/>
       <c r="BF34" s="116"/>
     </row>
-    <row r="35" spans="1:58" ht="48" x14ac:dyDescent="0.3">
-      <c r="A35" s="241" t="s">
+    <row r="35" spans="1:58" ht="48">
+      <c r="A35" s="231" t="s">
         <v>107</v>
       </c>
       <c r="B35" s="86" t="s">
@@ -7612,8 +7615,8 @@
       <c r="BE35" s="116"/>
       <c r="BF35" s="116"/>
     </row>
-    <row r="36" spans="1:58" ht="48" x14ac:dyDescent="0.3">
-      <c r="A36" s="235"/>
+    <row r="36" spans="1:58" ht="48">
+      <c r="A36" s="223"/>
       <c r="B36" s="29" t="s">
         <v>111</v>
       </c>
@@ -7708,8 +7711,8 @@
       <c r="BE36" s="116"/>
       <c r="BF36" s="116"/>
     </row>
-    <row r="37" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="263" t="s">
+    <row r="37" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A37" s="225" t="s">
         <v>114</v>
       </c>
       <c r="B37" s="29" t="s">
@@ -7806,8 +7809,8 @@
       <c r="BE37" s="116"/>
       <c r="BF37" s="116"/>
     </row>
-    <row r="38" spans="1:58" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="264"/>
+    <row r="38" spans="1:58" ht="30.6" customHeight="1">
+      <c r="A38" s="226"/>
       <c r="B38" s="29" t="s">
         <v>118</v>
       </c>
@@ -7902,8 +7905,8 @@
       <c r="BE38" s="116"/>
       <c r="BF38" s="116"/>
     </row>
-    <row r="39" spans="1:58" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="265"/>
+    <row r="39" spans="1:58" ht="30.6" customHeight="1">
+      <c r="A39" s="227"/>
       <c r="B39" s="29" t="s">
         <v>121</v>
       </c>
@@ -7998,7 +8001,7 @@
       <c r="BE39" s="116"/>
       <c r="BF39" s="116"/>
     </row>
-    <row r="40" spans="1:58" ht="58.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:58" ht="58.95" customHeight="1">
       <c r="A40" s="124" t="s">
         <v>124</v>
       </c>
@@ -8107,7 +8110,7 @@
       <c r="BE40" s="116"/>
       <c r="BF40" s="116"/>
     </row>
-    <row r="41" spans="1:58" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:58" ht="51.6" customHeight="1">
       <c r="A41" s="112" t="s">
         <v>128</v>
       </c>
@@ -8214,8 +8217,8 @@
       <c r="BE41" s="116"/>
       <c r="BF41" s="116"/>
     </row>
-    <row r="42" spans="1:58" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="222" t="s">
+    <row r="42" spans="1:58" ht="51.75" customHeight="1">
+      <c r="A42" s="230" t="s">
         <v>132</v>
       </c>
       <c r="B42" s="29" t="s">
@@ -8343,8 +8346,8 @@
       <c r="BE42" s="116"/>
       <c r="BF42" s="116"/>
     </row>
-    <row r="43" spans="1:58" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="222"/>
+    <row r="43" spans="1:58" ht="54.6" customHeight="1">
+      <c r="A43" s="230"/>
       <c r="B43" s="29" t="s">
         <v>136</v>
       </c>
@@ -8470,8 +8473,8 @@
       <c r="BE43" s="116"/>
       <c r="BF43" s="116"/>
     </row>
-    <row r="44" spans="1:58" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="222"/>
+    <row r="44" spans="1:58" ht="41.4" customHeight="1">
+      <c r="A44" s="230"/>
       <c r="B44" s="29" t="s">
         <v>139</v>
       </c>
@@ -8590,7 +8593,7 @@
         <v>409</v>
       </c>
       <c r="AO44" s="61" t="s">
-        <v>141</v>
+        <v>470</v>
       </c>
       <c r="AP44" s="116"/>
       <c r="AQ44" s="116"/>
@@ -8610,13 +8613,13 @@
       <c r="BE44" s="116"/>
       <c r="BF44" s="116"/>
     </row>
-    <row r="45" spans="1:58" ht="98.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="222"/>
+    <row r="45" spans="1:58" ht="98.4" customHeight="1">
+      <c r="A45" s="230"/>
       <c r="B45" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="C45" s="38" t="s">
         <v>142</v>
-      </c>
-      <c r="C45" s="38" t="s">
-        <v>143</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>17</v>
@@ -8731,7 +8734,7 @@
         <v>184</v>
       </c>
       <c r="AO45" s="61" t="s">
-        <v>144</v>
+        <v>471</v>
       </c>
       <c r="AP45" s="116"/>
       <c r="AQ45" s="116"/>
@@ -8753,13 +8756,13 @@
       <c r="BE45" s="116"/>
       <c r="BF45" s="116"/>
     </row>
-    <row r="46" spans="1:58" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="222"/>
+    <row r="46" spans="1:58" ht="67.95" customHeight="1">
+      <c r="A46" s="230"/>
       <c r="B46" s="29" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>17</v>
@@ -8875,7 +8878,7 @@
         <v>372</v>
       </c>
       <c r="AO46" s="61" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AP46" s="116"/>
       <c r="AQ46" s="116"/>
@@ -8897,15 +8900,15 @@
       <c r="BE46" s="116"/>
       <c r="BF46" s="116"/>
     </row>
-    <row r="47" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="229" t="s">
-        <v>148</v>
+    <row r="47" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A47" s="228" t="s">
+        <v>146</v>
       </c>
       <c r="B47" s="29" t="s">
         <v>133</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D47" s="135"/>
       <c r="E47" s="135"/>
@@ -8986,7 +8989,7 @@
         <v>30</v>
       </c>
       <c r="AO47" s="61" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AP47" s="116"/>
       <c r="AQ47" s="116"/>
@@ -9006,13 +9009,13 @@
       <c r="BE47" s="116"/>
       <c r="BF47" s="116"/>
     </row>
-    <row r="48" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="229"/>
+    <row r="48" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A48" s="228"/>
       <c r="B48" s="29" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C48" s="38" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D48" s="135"/>
       <c r="E48" s="135"/>
@@ -9104,7 +9107,7 @@
         <v>155</v>
       </c>
       <c r="AO48" s="61" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AP48" s="116"/>
       <c r="AQ48" s="116"/>
@@ -9124,13 +9127,13 @@
       <c r="BE48" s="116"/>
       <c r="BF48" s="116"/>
     </row>
-    <row r="49" spans="1:58" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="229"/>
+    <row r="49" spans="1:58" ht="51" customHeight="1">
+      <c r="A49" s="228"/>
       <c r="B49" s="29" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C49" s="38" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D49" s="135"/>
       <c r="E49" s="135"/>
@@ -9220,7 +9223,7 @@
         <v>110</v>
       </c>
       <c r="AO49" s="61" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AP49" s="116"/>
       <c r="AQ49" s="116"/>
@@ -9240,13 +9243,13 @@
       <c r="BE49" s="116"/>
       <c r="BF49" s="116"/>
     </row>
-    <row r="50" spans="1:58" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="229"/>
+    <row r="50" spans="1:58" ht="51.6" customHeight="1">
+      <c r="A50" s="228"/>
       <c r="B50" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C50" s="38" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D50" s="135"/>
       <c r="E50" s="135"/>
@@ -9325,7 +9328,7 @@
         <v>3</v>
       </c>
       <c r="AO50" s="61" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AP50" s="116"/>
       <c r="AQ50" s="116"/>
@@ -9345,13 +9348,13 @@
       <c r="BE50" s="116"/>
       <c r="BF50" s="116"/>
     </row>
-    <row r="51" spans="1:58" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="266"/>
+    <row r="51" spans="1:58" ht="40.950000000000003" customHeight="1">
+      <c r="A51" s="229"/>
       <c r="B51" s="30" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C51" s="99" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D51" s="136"/>
       <c r="E51" s="136"/>
@@ -9430,7 +9433,7 @@
         <v>60</v>
       </c>
       <c r="AO51" s="61" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AP51" s="116"/>
       <c r="AQ51" s="116"/>
@@ -9450,11 +9453,11 @@
       <c r="BE51" s="116"/>
       <c r="BF51" s="116"/>
     </row>
-    <row r="52" spans="1:58" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="242" t="s">
-        <v>162</v>
-      </c>
-      <c r="B52" s="243"/>
+    <row r="52" spans="1:58" ht="13.2" customHeight="1">
+      <c r="A52" s="232" t="s">
+        <v>160</v>
+      </c>
+      <c r="B52" s="233"/>
       <c r="C52" s="92"/>
       <c r="D52" s="5" t="s">
         <v>17</v>
@@ -9520,15 +9523,15 @@
       <c r="BE52" s="116"/>
       <c r="BF52" s="116"/>
     </row>
-    <row r="53" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="241" t="s">
+    <row r="53" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A53" s="231" t="s">
+        <v>161</v>
+      </c>
+      <c r="B53" s="86" t="s">
+        <v>162</v>
+      </c>
+      <c r="C53" s="41" t="s">
         <v>163</v>
-      </c>
-      <c r="B53" s="86" t="s">
-        <v>164</v>
-      </c>
-      <c r="C53" s="41" t="s">
-        <v>165</v>
       </c>
       <c r="D53" s="137" t="s">
         <v>17</v>
@@ -9596,7 +9599,7 @@
         <v>0.8</v>
       </c>
       <c r="AO53" s="91" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AP53" s="116"/>
       <c r="AQ53" s="116"/>
@@ -9616,13 +9619,13 @@
       <c r="BE53" s="116"/>
       <c r="BF53" s="116"/>
     </row>
-    <row r="54" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="235"/>
+    <row r="54" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A54" s="223"/>
       <c r="B54" s="29" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C54" s="38" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>17</v>
@@ -9690,7 +9693,7 @@
         <v>0.7</v>
       </c>
       <c r="AO54" s="61" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AP54" s="116"/>
       <c r="AQ54" s="116"/>
@@ -9710,15 +9713,15 @@
       <c r="BE54" s="116"/>
       <c r="BF54" s="116"/>
     </row>
-    <row r="55" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="234" t="s">
+    <row r="55" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A55" s="222" t="s">
+        <v>168</v>
+      </c>
+      <c r="B55" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="C55" s="38" t="s">
         <v>170</v>
-      </c>
-      <c r="B55" s="43" t="s">
-        <v>171</v>
-      </c>
-      <c r="C55" s="38" t="s">
-        <v>172</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>17</v>
@@ -9786,7 +9789,7 @@
         <v>0.6</v>
       </c>
       <c r="AO55" s="61" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AP55" s="116"/>
       <c r="AQ55" s="116"/>
@@ -9806,13 +9809,13 @@
       <c r="BE55" s="116"/>
       <c r="BF55" s="116"/>
     </row>
-    <row r="56" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="234"/>
+    <row r="56" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A56" s="222"/>
       <c r="B56" s="29" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>17</v>
@@ -9901,7 +9904,7 @@
         <v>4</v>
       </c>
       <c r="AO56" s="61" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AP56" s="116"/>
       <c r="AQ56" s="116"/>
@@ -9921,13 +9924,13 @@
       <c r="BE56" s="116"/>
       <c r="BF56" s="116"/>
     </row>
-    <row r="57" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="234"/>
+    <row r="57" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A57" s="222"/>
       <c r="B57" s="29" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C57" s="38" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>17</v>
@@ -9995,7 +9998,7 @@
         <v>0.8</v>
       </c>
       <c r="AO57" s="61" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AP57" s="116"/>
       <c r="AQ57" s="116"/>
@@ -10015,13 +10018,13 @@
       <c r="BE57" s="116"/>
       <c r="BF57" s="116"/>
     </row>
-    <row r="58" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="234"/>
+    <row r="58" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A58" s="222"/>
       <c r="B58" s="29" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C58" s="38" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>17</v>
@@ -10089,7 +10092,7 @@
         <v>0.7</v>
       </c>
       <c r="AO58" s="61" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AP58" s="116"/>
       <c r="AQ58" s="116"/>
@@ -10109,15 +10112,15 @@
       <c r="BE58" s="116"/>
       <c r="BF58" s="116"/>
     </row>
-    <row r="59" spans="1:58" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:58" ht="60" customHeight="1">
       <c r="A59" s="74" t="s">
+        <v>181</v>
+      </c>
+      <c r="B59" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="C59" s="38" t="s">
         <v>183</v>
-      </c>
-      <c r="B59" s="29" t="s">
-        <v>184</v>
-      </c>
-      <c r="C59" s="38" t="s">
-        <v>185</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>17</v>
@@ -10200,7 +10203,7 @@
         <v>4</v>
       </c>
       <c r="AO59" s="61" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AP59" s="116"/>
       <c r="AQ59" s="116"/>
@@ -10220,15 +10223,15 @@
       <c r="BE59" s="116"/>
       <c r="BF59" s="116"/>
     </row>
-    <row r="60" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="234" t="s">
+    <row r="60" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A60" s="222" t="s">
+        <v>185</v>
+      </c>
+      <c r="B60" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="C60" s="38" t="s">
         <v>187</v>
-      </c>
-      <c r="B60" s="29" t="s">
-        <v>188</v>
-      </c>
-      <c r="C60" s="38" t="s">
-        <v>189</v>
       </c>
       <c r="D60" s="135"/>
       <c r="E60" s="135"/>
@@ -10319,7 +10322,7 @@
         <v>5</v>
       </c>
       <c r="AO60" s="61" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AP60" s="116"/>
       <c r="AQ60" s="116"/>
@@ -10339,13 +10342,13 @@
       <c r="BE60" s="116"/>
       <c r="BF60" s="116"/>
     </row>
-    <row r="61" spans="1:58" ht="70.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="235"/>
+    <row r="61" spans="1:58" ht="70.95" customHeight="1">
+      <c r="A61" s="223"/>
       <c r="B61" s="29" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C61" s="38" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D61" s="135"/>
       <c r="E61" s="135"/>
@@ -10437,7 +10440,7 @@
         <v>2</v>
       </c>
       <c r="AO61" s="61" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AP61" s="116"/>
       <c r="AQ61" s="116"/>
@@ -10457,13 +10460,13 @@
       <c r="BE61" s="116"/>
       <c r="BF61" s="116"/>
     </row>
-    <row r="62" spans="1:58" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="261"/>
+    <row r="62" spans="1:58" ht="33.6" customHeight="1">
+      <c r="A62" s="224"/>
       <c r="B62" s="30" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C62" s="99" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D62" s="136"/>
       <c r="E62" s="136"/>
@@ -10560,7 +10563,7 @@
         <v>67</v>
       </c>
       <c r="AO62" s="101" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AP62" s="116"/>
       <c r="AQ62" s="116"/>
@@ -10580,11 +10583,11 @@
       <c r="BE62" s="116"/>
       <c r="BF62" s="116"/>
     </row>
-    <row r="63" spans="1:58" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="242" t="s">
-        <v>197</v>
-      </c>
-      <c r="B63" s="243"/>
+    <row r="63" spans="1:58" ht="13.2" customHeight="1">
+      <c r="A63" s="232" t="s">
+        <v>195</v>
+      </c>
+      <c r="B63" s="233"/>
       <c r="C63" s="92"/>
       <c r="D63" s="5" t="s">
         <v>17</v>
@@ -10650,15 +10653,15 @@
       <c r="BE63" s="116"/>
       <c r="BF63" s="116"/>
     </row>
-    <row r="64" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="241" t="s">
+    <row r="64" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A64" s="231" t="s">
+        <v>196</v>
+      </c>
+      <c r="B64" s="86" t="s">
+        <v>197</v>
+      </c>
+      <c r="C64" s="41" t="s">
         <v>198</v>
-      </c>
-      <c r="B64" s="86" t="s">
-        <v>199</v>
-      </c>
-      <c r="C64" s="41" t="s">
-        <v>200</v>
       </c>
       <c r="D64" s="137" t="s">
         <v>17</v>
@@ -10730,7 +10733,7 @@
         <v>0.7</v>
       </c>
       <c r="AO64" s="91" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AP64" s="116"/>
       <c r="AQ64" s="116"/>
@@ -10750,13 +10753,13 @@
       <c r="BE64" s="116"/>
       <c r="BF64" s="116"/>
     </row>
-    <row r="65" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="235"/>
+    <row r="65" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A65" s="223"/>
       <c r="B65" s="29" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C65" s="38" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D65" s="9" t="s">
         <v>17</v>
@@ -10826,7 +10829,7 @@
         <v>0.7</v>
       </c>
       <c r="AO65" s="61" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AP65" s="116"/>
       <c r="AQ65" s="116"/>
@@ -10846,15 +10849,15 @@
       <c r="BE65" s="116"/>
       <c r="BF65" s="116"/>
     </row>
-    <row r="66" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:58" ht="43.5" customHeight="1">
       <c r="A66" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="B66" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="C66" s="38" t="s">
         <v>205</v>
-      </c>
-      <c r="B66" s="29" t="s">
-        <v>206</v>
-      </c>
-      <c r="C66" s="38" t="s">
-        <v>207</v>
       </c>
       <c r="D66" s="9" t="s">
         <v>17</v>
@@ -10922,7 +10925,7 @@
         <v>0.75</v>
       </c>
       <c r="AO66" s="61" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AP66" s="116"/>
       <c r="AQ66" s="116"/>
@@ -10942,15 +10945,15 @@
       <c r="BE66" s="116"/>
       <c r="BF66" s="116"/>
     </row>
-    <row r="67" spans="1:58" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:58" ht="78.599999999999994" customHeight="1">
       <c r="A67" s="126" t="s">
+        <v>207</v>
+      </c>
+      <c r="B67" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="C67" s="38" t="s">
         <v>209</v>
-      </c>
-      <c r="B67" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="C67" s="38" t="s">
-        <v>211</v>
       </c>
       <c r="D67" s="9" t="s">
         <v>17</v>
@@ -11049,7 +11052,7 @@
         <v>276</v>
       </c>
       <c r="AO67" s="61" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AP67" s="116"/>
       <c r="AQ67" s="116"/>
@@ -11069,15 +11072,15 @@
       <c r="BE67" s="116"/>
       <c r="BF67" s="116"/>
     </row>
-    <row r="68" spans="1:58" ht="84" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:58" ht="72">
       <c r="A68" s="126" t="s">
+        <v>211</v>
+      </c>
+      <c r="B68" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="C68" s="38" t="s">
         <v>213</v>
-      </c>
-      <c r="B68" s="29" t="s">
-        <v>214</v>
-      </c>
-      <c r="C68" s="38" t="s">
-        <v>215</v>
       </c>
       <c r="D68" s="9" t="s">
         <v>17</v>
@@ -11170,7 +11173,7 @@
         <v>141</v>
       </c>
       <c r="AO68" s="61" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AP68" s="116"/>
       <c r="AQ68" s="116"/>
@@ -11190,15 +11193,15 @@
       <c r="BE68" s="116"/>
       <c r="BF68" s="116"/>
     </row>
-    <row r="69" spans="1:58" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:58" ht="69.75" customHeight="1">
       <c r="A69" s="126" t="s">
+        <v>215</v>
+      </c>
+      <c r="B69" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="C69" s="38" t="s">
         <v>217</v>
-      </c>
-      <c r="B69" s="29" t="s">
-        <v>218</v>
-      </c>
-      <c r="C69" s="38" t="s">
-        <v>219</v>
       </c>
       <c r="D69" s="9" t="s">
         <v>17</v>
@@ -11270,7 +11273,7 @@
         <v>0.75</v>
       </c>
       <c r="AO69" s="61" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AP69" s="116"/>
       <c r="AQ69" s="116"/>
@@ -11290,15 +11293,15 @@
       <c r="BE69" s="116"/>
       <c r="BF69" s="116"/>
     </row>
-    <row r="70" spans="1:58" ht="103.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:58" ht="103.2" customHeight="1">
       <c r="A70" s="74" t="s">
+        <v>219</v>
+      </c>
+      <c r="B70" s="29" t="s">
+        <v>220</v>
+      </c>
+      <c r="C70" s="38" t="s">
         <v>221</v>
-      </c>
-      <c r="B70" s="29" t="s">
-        <v>222</v>
-      </c>
-      <c r="C70" s="38" t="s">
-        <v>223</v>
       </c>
       <c r="D70" s="9" t="s">
         <v>17</v>
@@ -11398,7 +11401,7 @@
         <v>7</v>
       </c>
       <c r="AO70" s="61" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AP70" s="116"/>
       <c r="AQ70" s="116"/>
@@ -11418,15 +11421,15 @@
       <c r="BE70" s="116"/>
       <c r="BF70" s="116"/>
     </row>
-    <row r="71" spans="1:58" ht="88.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:58" ht="88.95" customHeight="1">
       <c r="A71" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="B71" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="C71" s="38" t="s">
         <v>225</v>
-      </c>
-      <c r="B71" s="29" t="s">
-        <v>226</v>
-      </c>
-      <c r="C71" s="38" t="s">
-        <v>227</v>
       </c>
       <c r="D71" s="9" t="s">
         <v>17</v>
@@ -11537,7 +11540,7 @@
         <v>11</v>
       </c>
       <c r="AO71" s="61" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AP71" s="116"/>
       <c r="AQ71" s="116"/>
@@ -11557,15 +11560,15 @@
       <c r="BE71" s="116"/>
       <c r="BF71" s="116"/>
     </row>
-    <row r="72" spans="1:58" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="222" t="s">
+    <row r="72" spans="1:58" ht="52.2" customHeight="1">
+      <c r="A72" s="230" t="s">
+        <v>227</v>
+      </c>
+      <c r="B72" s="80" t="s">
+        <v>228</v>
+      </c>
+      <c r="C72" s="38" t="s">
         <v>229</v>
-      </c>
-      <c r="B72" s="80" t="s">
-        <v>230</v>
-      </c>
-      <c r="C72" s="38" t="s">
-        <v>231</v>
       </c>
       <c r="D72" s="135"/>
       <c r="E72" s="135"/>
@@ -11633,7 +11636,7 @@
         <v>0.75</v>
       </c>
       <c r="AO72" s="62" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AP72" s="116"/>
       <c r="AQ72" s="116"/>
@@ -11653,13 +11656,13 @@
       <c r="BE72" s="116"/>
       <c r="BF72" s="116"/>
     </row>
-    <row r="73" spans="1:58" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="222"/>
+    <row r="73" spans="1:58" ht="63" customHeight="1">
+      <c r="A73" s="230"/>
       <c r="B73" s="80" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C73" s="38" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D73" s="135"/>
       <c r="E73" s="135"/>
@@ -11742,7 +11745,7 @@
         <v>4000</v>
       </c>
       <c r="AO73" s="62" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AP73" s="116"/>
       <c r="AQ73" s="116"/>
@@ -11762,15 +11765,15 @@
       <c r="BE73" s="116"/>
       <c r="BF73" s="116"/>
     </row>
-    <row r="74" spans="1:58" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:58" ht="53.4" customHeight="1">
       <c r="A74" s="74" t="s">
+        <v>234</v>
+      </c>
+      <c r="B74" s="29" t="s">
+        <v>235</v>
+      </c>
+      <c r="C74" s="38" t="s">
         <v>236</v>
-      </c>
-      <c r="B74" s="29" t="s">
-        <v>237</v>
-      </c>
-      <c r="C74" s="38" t="s">
-        <v>238</v>
       </c>
       <c r="D74" s="135"/>
       <c r="E74" s="135"/>
@@ -11844,7 +11847,7 @@
         <v>2</v>
       </c>
       <c r="AO74" s="61" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AP74" s="116"/>
       <c r="AQ74" s="116"/>
@@ -11864,15 +11867,15 @@
       <c r="BE74" s="116"/>
       <c r="BF74" s="116"/>
     </row>
-    <row r="75" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="222" t="s">
+    <row r="75" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A75" s="230" t="s">
+        <v>238</v>
+      </c>
+      <c r="B75" s="29" t="s">
+        <v>239</v>
+      </c>
+      <c r="C75" s="38" t="s">
         <v>240</v>
-      </c>
-      <c r="B75" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="C75" s="38" t="s">
-        <v>242</v>
       </c>
       <c r="D75" s="135"/>
       <c r="E75" s="135"/>
@@ -11948,7 +11951,7 @@
         <v>0.5</v>
       </c>
       <c r="AO75" s="61" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AP75" s="116"/>
       <c r="AQ75" s="116"/>
@@ -11968,13 +11971,13 @@
       <c r="BE75" s="116"/>
       <c r="BF75" s="116"/>
     </row>
-    <row r="76" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="229"/>
+    <row r="76" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A76" s="228"/>
       <c r="B76" s="29" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C76" s="38" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D76" s="135"/>
       <c r="E76" s="135"/>
@@ -12052,7 +12055,7 @@
         <v>0.8</v>
       </c>
       <c r="AO76" s="61" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AP76" s="116"/>
       <c r="AQ76" s="116"/>
@@ -12072,13 +12075,13 @@
       <c r="BE76" s="116"/>
       <c r="BF76" s="116"/>
     </row>
-    <row r="77" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="229"/>
+    <row r="77" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A77" s="228"/>
       <c r="B77" s="29" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C77" s="38" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D77" s="135"/>
       <c r="E77" s="135"/>
@@ -12156,7 +12159,7 @@
         <v>0.8</v>
       </c>
       <c r="AO77" s="61" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AP77" s="116"/>
       <c r="AQ77" s="116"/>
@@ -12176,13 +12179,13 @@
       <c r="BE77" s="116"/>
       <c r="BF77" s="116"/>
     </row>
-    <row r="78" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="229"/>
+    <row r="78" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A78" s="228"/>
       <c r="B78" s="29" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C78" s="38" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D78" s="135"/>
       <c r="E78" s="135"/>
@@ -12260,7 +12263,7 @@
         <v>0.9</v>
       </c>
       <c r="AO78" s="61" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AP78" s="116"/>
       <c r="AQ78" s="116"/>
@@ -12280,13 +12283,13 @@
       <c r="BE78" s="116"/>
       <c r="BF78" s="116"/>
     </row>
-    <row r="79" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="229"/>
+    <row r="79" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A79" s="228"/>
       <c r="B79" s="29" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C79" s="38" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D79" s="135"/>
       <c r="E79" s="135"/>
@@ -12364,7 +12367,7 @@
         <v>0.7</v>
       </c>
       <c r="AO79" s="61" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AP79" s="116"/>
       <c r="AQ79" s="116"/>
@@ -12384,13 +12387,13 @@
       <c r="BE79" s="116"/>
       <c r="BF79" s="116"/>
     </row>
-    <row r="80" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="229"/>
+    <row r="80" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A80" s="228"/>
       <c r="B80" s="29" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C80" s="38" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D80" s="135"/>
       <c r="E80" s="135"/>
@@ -12468,7 +12471,7 @@
         <v>0.8</v>
       </c>
       <c r="AO80" s="61" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AP80" s="116"/>
       <c r="AQ80" s="116"/>
@@ -12488,13 +12491,13 @@
       <c r="BE80" s="116"/>
       <c r="BF80" s="116"/>
     </row>
-    <row r="81" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="229"/>
+    <row r="81" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A81" s="228"/>
       <c r="B81" s="29" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C81" s="38" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D81" s="135"/>
       <c r="E81" s="135"/>
@@ -12572,7 +12575,7 @@
         <v>0.8</v>
       </c>
       <c r="AO81" s="61" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AP81" s="116"/>
       <c r="AQ81" s="116"/>
@@ -12592,15 +12595,15 @@
       <c r="BE81" s="116"/>
       <c r="BF81" s="116"/>
     </row>
-    <row r="82" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="222" t="s">
+    <row r="82" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A82" s="230" t="s">
+        <v>260</v>
+      </c>
+      <c r="B82" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="C82" s="38" t="s">
         <v>262</v>
-      </c>
-      <c r="B82" s="29" t="s">
-        <v>263</v>
-      </c>
-      <c r="C82" s="38" t="s">
-        <v>264</v>
       </c>
       <c r="D82" s="135"/>
       <c r="E82" s="135"/>
@@ -12682,7 +12685,7 @@
         <v>1500</v>
       </c>
       <c r="AO82" s="61" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AP82" s="116"/>
       <c r="AQ82" s="116"/>
@@ -12702,13 +12705,13 @@
       <c r="BE82" s="116"/>
       <c r="BF82" s="116"/>
     </row>
-    <row r="83" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="222"/>
+    <row r="83" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A83" s="230"/>
       <c r="B83" s="29" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C83" s="38" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D83" s="135"/>
       <c r="E83" s="135"/>
@@ -12789,7 +12792,7 @@
         <v>4</v>
       </c>
       <c r="AO83" s="61" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AP83" s="116"/>
       <c r="AQ83" s="116"/>
@@ -12809,15 +12812,15 @@
       <c r="BE83" s="116"/>
       <c r="BF83" s="116"/>
     </row>
-    <row r="84" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="222" t="s">
+    <row r="84" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A84" s="230" t="s">
+        <v>267</v>
+      </c>
+      <c r="B84" s="29" t="s">
+        <v>268</v>
+      </c>
+      <c r="C84" s="38" t="s">
         <v>269</v>
-      </c>
-      <c r="B84" s="29" t="s">
-        <v>270</v>
-      </c>
-      <c r="C84" s="38" t="s">
-        <v>271</v>
       </c>
       <c r="D84" s="135"/>
       <c r="E84" s="135"/>
@@ -12893,7 +12896,7 @@
         <v>40</v>
       </c>
       <c r="AO84" s="61" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AP84" s="116"/>
       <c r="AQ84" s="116"/>
@@ -12913,13 +12916,13 @@
       <c r="BE84" s="116"/>
       <c r="BF84" s="116"/>
     </row>
-    <row r="85" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="222"/>
+    <row r="85" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A85" s="230"/>
       <c r="B85" s="29" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C85" s="38" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D85" s="135"/>
       <c r="E85" s="135"/>
@@ -12995,7 +12998,7 @@
         <v>32</v>
       </c>
       <c r="AO85" s="61" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AP85" s="116"/>
       <c r="AQ85" s="116"/>
@@ -13015,13 +13018,13 @@
       <c r="BE85" s="116"/>
       <c r="BF85" s="116"/>
     </row>
-    <row r="86" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="222"/>
+    <row r="86" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A86" s="230"/>
       <c r="B86" s="29" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C86" s="38" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D86" s="135"/>
       <c r="E86" s="135"/>
@@ -13097,7 +13100,7 @@
         <v>800</v>
       </c>
       <c r="AO86" s="61" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AP86" s="116"/>
       <c r="AQ86" s="116"/>
@@ -13117,13 +13120,13 @@
       <c r="BE86" s="116"/>
       <c r="BF86" s="116"/>
     </row>
-    <row r="87" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="222"/>
+    <row r="87" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A87" s="230"/>
       <c r="B87" s="29" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C87" s="38" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D87" s="135"/>
       <c r="E87" s="135"/>
@@ -13199,7 +13202,7 @@
         <v>40</v>
       </c>
       <c r="AO87" s="61" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AP87" s="116"/>
       <c r="AQ87" s="116"/>
@@ -13219,13 +13222,13 @@
       <c r="BE87" s="116"/>
       <c r="BF87" s="116"/>
     </row>
-    <row r="88" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="222"/>
+    <row r="88" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A88" s="230"/>
       <c r="B88" s="29" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C88" s="38" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D88" s="135"/>
       <c r="E88" s="135"/>
@@ -13301,7 +13304,7 @@
         <v>4</v>
       </c>
       <c r="AO88" s="61" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AP88" s="116"/>
       <c r="AQ88" s="116"/>
@@ -13321,13 +13324,13 @@
       <c r="BE88" s="116"/>
       <c r="BF88" s="116"/>
     </row>
-    <row r="89" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="222"/>
+    <row r="89" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A89" s="230"/>
       <c r="B89" s="50" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C89" s="38" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D89" s="135"/>
       <c r="E89" s="135"/>
@@ -13403,7 +13406,7 @@
         <v>4</v>
       </c>
       <c r="AO89" s="61" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AP89" s="116"/>
       <c r="AQ89" s="116"/>
@@ -13423,15 +13426,15 @@
       <c r="BE89" s="116"/>
       <c r="BF89" s="116"/>
     </row>
-    <row r="90" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="222" t="s">
+    <row r="90" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A90" s="230" t="s">
+        <v>286</v>
+      </c>
+      <c r="B90" s="29" t="s">
+        <v>287</v>
+      </c>
+      <c r="C90" s="38" t="s">
         <v>288</v>
-      </c>
-      <c r="B90" s="29" t="s">
-        <v>289</v>
-      </c>
-      <c r="C90" s="38" t="s">
-        <v>290</v>
       </c>
       <c r="D90" s="135"/>
       <c r="E90" s="135"/>
@@ -13508,7 +13511,7 @@
         <v>50</v>
       </c>
       <c r="AO90" s="61" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AP90" s="116"/>
       <c r="AQ90" s="116"/>
@@ -13528,13 +13531,13 @@
       <c r="BE90" s="116"/>
       <c r="BF90" s="116"/>
     </row>
-    <row r="91" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="222"/>
+    <row r="91" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A91" s="230"/>
       <c r="B91" s="29" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C91" s="38" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D91" s="135"/>
       <c r="E91" s="135"/>
@@ -13611,7 +13614,7 @@
         <v>40</v>
       </c>
       <c r="AO91" s="61" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AP91" s="116"/>
       <c r="AQ91" s="116"/>
@@ -13631,13 +13634,13 @@
       <c r="BE91" s="116"/>
       <c r="BF91" s="116"/>
     </row>
-    <row r="92" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="222"/>
+    <row r="92" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A92" s="230"/>
       <c r="B92" s="29" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C92" s="38" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D92" s="135"/>
       <c r="E92" s="135"/>
@@ -13714,7 +13717,7 @@
         <v>40</v>
       </c>
       <c r="AO92" s="61" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AP92" s="116"/>
       <c r="AQ92" s="116"/>
@@ -13734,13 +13737,13 @@
       <c r="BE92" s="116"/>
       <c r="BF92" s="116"/>
     </row>
-    <row r="93" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="222"/>
+    <row r="93" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A93" s="230"/>
       <c r="B93" s="29" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C93" s="38" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D93" s="135"/>
       <c r="E93" s="135"/>
@@ -13822,7 +13825,7 @@
         <v>1120</v>
       </c>
       <c r="AO93" s="61" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AP93" s="116"/>
       <c r="AQ93" s="116"/>
@@ -13842,13 +13845,13 @@
       <c r="BE93" s="116"/>
       <c r="BF93" s="116"/>
     </row>
-    <row r="94" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="222"/>
+    <row r="94" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A94" s="230"/>
       <c r="B94" s="29" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C94" s="38" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D94" s="135"/>
       <c r="E94" s="135"/>
@@ -13932,7 +13935,7 @@
         <v>1032</v>
       </c>
       <c r="AO94" s="61" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AP94" s="116"/>
       <c r="AQ94" s="116"/>
@@ -13952,13 +13955,13 @@
       <c r="BE94" s="116"/>
       <c r="BF94" s="116"/>
     </row>
-    <row r="95" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="222"/>
+    <row r="95" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A95" s="230"/>
       <c r="B95" s="29" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C95" s="38" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D95" s="135"/>
       <c r="E95" s="135"/>
@@ -14042,7 +14045,7 @@
         <v>896</v>
       </c>
       <c r="AO95" s="61" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AP95" s="116"/>
       <c r="AQ95" s="116"/>
@@ -14062,15 +14065,15 @@
       <c r="BE95" s="116"/>
       <c r="BF95" s="116"/>
     </row>
-    <row r="96" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="229" t="s">
+    <row r="96" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A96" s="228" t="s">
+        <v>305</v>
+      </c>
+      <c r="B96" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="C96" s="38" t="s">
         <v>307</v>
-      </c>
-      <c r="B96" s="29" t="s">
-        <v>308</v>
-      </c>
-      <c r="C96" s="38" t="s">
-        <v>309</v>
       </c>
       <c r="D96" s="135"/>
       <c r="E96" s="10" t="s">
@@ -14138,7 +14141,7 @@
         <v>0.9</v>
       </c>
       <c r="AO96" s="65" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AP96" s="116"/>
       <c r="AQ96" s="116"/>
@@ -14158,13 +14161,13 @@
       <c r="BE96" s="116"/>
       <c r="BF96" s="116"/>
     </row>
-    <row r="97" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="229"/>
+    <row r="97" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A97" s="228"/>
       <c r="B97" s="29" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C97" s="38" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D97" s="135"/>
       <c r="E97" s="10" t="s">
@@ -14240,7 +14243,7 @@
         <v>10</v>
       </c>
       <c r="AO97" s="65" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AP97" s="116"/>
       <c r="AQ97" s="116"/>
@@ -14260,13 +14263,13 @@
       <c r="BE97" s="116"/>
       <c r="BF97" s="116"/>
     </row>
-    <row r="98" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="229"/>
+    <row r="98" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A98" s="228"/>
       <c r="B98" s="29" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C98" s="38" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D98" s="135"/>
       <c r="E98" s="10" t="s">
@@ -14334,7 +14337,7 @@
         <v>0.8</v>
       </c>
       <c r="AO98" s="65" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AP98" s="116"/>
       <c r="AQ98" s="116"/>
@@ -14354,15 +14357,15 @@
       <c r="BE98" s="116"/>
       <c r="BF98" s="116"/>
     </row>
-    <row r="99" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:58" ht="43.5" customHeight="1">
       <c r="A99" s="112" t="s">
+        <v>315</v>
+      </c>
+      <c r="B99" s="29" t="s">
+        <v>316</v>
+      </c>
+      <c r="C99" s="38" t="s">
         <v>317</v>
-      </c>
-      <c r="B99" s="29" t="s">
-        <v>318</v>
-      </c>
-      <c r="C99" s="38" t="s">
-        <v>319</v>
       </c>
       <c r="D99" s="135"/>
       <c r="E99" s="10" t="s">
@@ -14441,7 +14444,7 @@
         <v>30</v>
       </c>
       <c r="AO99" s="61" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AP99" s="116"/>
       <c r="AQ99" s="116"/>
@@ -14461,15 +14464,15 @@
       <c r="BE99" s="116"/>
       <c r="BF99" s="116"/>
     </row>
-    <row r="100" spans="1:58" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:58" ht="64.95" customHeight="1">
       <c r="A100" s="112" t="s">
+        <v>319</v>
+      </c>
+      <c r="B100" s="29" t="s">
+        <v>320</v>
+      </c>
+      <c r="C100" s="38" t="s">
         <v>321</v>
-      </c>
-      <c r="B100" s="29" t="s">
-        <v>322</v>
-      </c>
-      <c r="C100" s="38" t="s">
-        <v>323</v>
       </c>
       <c r="D100" s="135"/>
       <c r="E100" s="10" t="s">
@@ -14547,7 +14550,7 @@
         <v>5</v>
       </c>
       <c r="AO100" s="61" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AP100" s="116"/>
       <c r="AQ100" s="116"/>
@@ -14567,15 +14570,15 @@
       <c r="BE100" s="116"/>
       <c r="BF100" s="116"/>
     </row>
-    <row r="101" spans="1:58" ht="70.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:58" ht="70.95" customHeight="1">
       <c r="A101" s="112" t="s">
+        <v>323</v>
+      </c>
+      <c r="B101" s="29" t="s">
+        <v>324</v>
+      </c>
+      <c r="C101" s="38" t="s">
         <v>325</v>
-      </c>
-      <c r="B101" s="29" t="s">
-        <v>326</v>
-      </c>
-      <c r="C101" s="38" t="s">
-        <v>327</v>
       </c>
       <c r="D101" s="135"/>
       <c r="E101" s="10" t="s">
@@ -14653,7 +14656,7 @@
         <v>4</v>
       </c>
       <c r="AO101" s="61" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AP101" s="116"/>
       <c r="AQ101" s="116"/>
@@ -14673,15 +14676,15 @@
       <c r="BE101" s="116"/>
       <c r="BF101" s="116"/>
     </row>
-    <row r="102" spans="1:58" ht="91.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:58" ht="91.2" customHeight="1">
       <c r="A102" s="127" t="s">
+        <v>327</v>
+      </c>
+      <c r="B102" s="46" t="s">
+        <v>328</v>
+      </c>
+      <c r="C102" s="38" t="s">
         <v>329</v>
-      </c>
-      <c r="B102" s="46" t="s">
-        <v>330</v>
-      </c>
-      <c r="C102" s="38" t="s">
-        <v>331</v>
       </c>
       <c r="D102" s="135"/>
       <c r="E102" s="10" t="s">
@@ -14762,7 +14765,7 @@
         <v>2</v>
       </c>
       <c r="AO102" s="64" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AP102" s="116"/>
       <c r="AQ102" s="116"/>
@@ -14782,15 +14785,15 @@
       <c r="BE102" s="116"/>
       <c r="BF102" s="116"/>
     </row>
-    <row r="103" spans="1:58" ht="84" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:58" ht="72">
       <c r="A103" s="112" t="s">
+        <v>331</v>
+      </c>
+      <c r="B103" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="C103" s="38" t="s">
         <v>333</v>
-      </c>
-      <c r="B103" s="29" t="s">
-        <v>334</v>
-      </c>
-      <c r="C103" s="38" t="s">
-        <v>335</v>
       </c>
       <c r="D103" s="135"/>
       <c r="E103" s="10" t="s">
@@ -14873,7 +14876,7 @@
         <v>4</v>
       </c>
       <c r="AO103" s="64" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AP103" s="116"/>
       <c r="AQ103" s="116"/>
@@ -14893,15 +14896,15 @@
       <c r="BE103" s="116"/>
       <c r="BF103" s="116"/>
     </row>
-    <row r="104" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:58" ht="43.5" customHeight="1">
       <c r="A104" s="125" t="s">
+        <v>335</v>
+      </c>
+      <c r="B104" s="30" t="s">
+        <v>336</v>
+      </c>
+      <c r="C104" s="99" t="s">
         <v>337</v>
-      </c>
-      <c r="B104" s="30" t="s">
-        <v>338</v>
-      </c>
-      <c r="C104" s="99" t="s">
-        <v>339</v>
       </c>
       <c r="D104" s="136"/>
       <c r="E104" s="6" t="s">
@@ -14985,7 +14988,7 @@
         <v>301</v>
       </c>
       <c r="AO104" s="102" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AP104" s="116"/>
       <c r="AQ104" s="116"/>
@@ -15005,11 +15008,11 @@
       <c r="BE104" s="116"/>
       <c r="BF104" s="116"/>
     </row>
-    <row r="105" spans="1:58" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="242" t="s">
-        <v>341</v>
-      </c>
-      <c r="B105" s="243"/>
+    <row r="105" spans="1:58" ht="15.45" customHeight="1">
+      <c r="A105" s="232" t="s">
+        <v>339</v>
+      </c>
+      <c r="B105" s="233"/>
       <c r="C105" s="92"/>
       <c r="D105" s="5" t="s">
         <v>17</v>
@@ -15075,15 +15078,15 @@
       <c r="BE105" s="116"/>
       <c r="BF105" s="116"/>
     </row>
-    <row r="106" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="260" t="s">
+    <row r="106" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A106" s="235" t="s">
+        <v>340</v>
+      </c>
+      <c r="B106" s="86" t="s">
+        <v>341</v>
+      </c>
+      <c r="C106" s="41" t="s">
         <v>342</v>
-      </c>
-      <c r="B106" s="86" t="s">
-        <v>343</v>
-      </c>
-      <c r="C106" s="41" t="s">
-        <v>344</v>
       </c>
       <c r="D106" s="137" t="s">
         <v>17</v>
@@ -15167,7 +15170,7 @@
         <v>0.8</v>
       </c>
       <c r="AO106" s="91" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AP106" s="116"/>
       <c r="AQ106" s="116"/>
@@ -15187,13 +15190,13 @@
       <c r="BE106" s="116"/>
       <c r="BF106" s="116"/>
     </row>
-    <row r="107" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="229"/>
+    <row r="107" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A107" s="228"/>
       <c r="B107" s="29" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C107" s="38" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D107" s="9" t="s">
         <v>17</v>
@@ -15277,7 +15280,7 @@
         <v>0.8</v>
       </c>
       <c r="AO107" s="61" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AP107" s="116"/>
       <c r="AQ107" s="116"/>
@@ -15297,13 +15300,13 @@
       <c r="BE107" s="116"/>
       <c r="BF107" s="116"/>
     </row>
-    <row r="108" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="229"/>
+    <row r="108" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A108" s="228"/>
       <c r="B108" s="29" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C108" s="38" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D108" s="9" t="s">
         <v>17</v>
@@ -15387,7 +15390,7 @@
         <v>0.7</v>
       </c>
       <c r="AO108" s="61" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AP108" s="116"/>
       <c r="AQ108" s="116"/>
@@ -15407,13 +15410,13 @@
       <c r="BE108" s="116"/>
       <c r="BF108" s="116"/>
     </row>
-    <row r="109" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="229"/>
+    <row r="109" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A109" s="228"/>
       <c r="B109" s="29" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C109" s="38" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D109" s="9" t="s">
         <v>17</v>
@@ -15497,7 +15500,7 @@
         <v>0.7</v>
       </c>
       <c r="AO109" s="61" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AP109" s="116"/>
       <c r="AQ109" s="116"/>
@@ -15517,13 +15520,13 @@
       <c r="BE109" s="116"/>
       <c r="BF109" s="116"/>
     </row>
-    <row r="110" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="229"/>
+    <row r="110" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A110" s="228"/>
       <c r="B110" s="29" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C110" s="38" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D110" s="9" t="s">
         <v>17</v>
@@ -15607,7 +15610,7 @@
         <v>0.7</v>
       </c>
       <c r="AO110" s="61" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AP110" s="116"/>
       <c r="AQ110" s="116"/>
@@ -15627,15 +15630,15 @@
       <c r="BE110" s="116"/>
       <c r="BF110" s="116"/>
     </row>
-    <row r="111" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="222" t="s">
+    <row r="111" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A111" s="230" t="s">
+        <v>356</v>
+      </c>
+      <c r="B111" s="29" t="s">
+        <v>357</v>
+      </c>
+      <c r="C111" s="38" t="s">
         <v>358</v>
-      </c>
-      <c r="B111" s="29" t="s">
-        <v>359</v>
-      </c>
-      <c r="C111" s="38" t="s">
-        <v>360</v>
       </c>
       <c r="D111" s="135"/>
       <c r="E111" s="135"/>
@@ -15717,7 +15720,7 @@
         <v>0.8</v>
       </c>
       <c r="AO111" s="61" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AP111" s="116"/>
       <c r="AQ111" s="116"/>
@@ -15737,13 +15740,13 @@
       <c r="BE111" s="116"/>
       <c r="BF111" s="116"/>
     </row>
-    <row r="112" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="222"/>
+    <row r="112" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A112" s="230"/>
       <c r="B112" s="52" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C112" s="53" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D112" s="135"/>
       <c r="E112" s="135"/>
@@ -15825,7 +15828,7 @@
         <v>0.8</v>
       </c>
       <c r="AO112" s="61" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AP112" s="116"/>
       <c r="AQ112" s="116"/>
@@ -15845,15 +15848,15 @@
       <c r="BE112" s="116"/>
       <c r="BF112" s="116"/>
     </row>
-    <row r="113" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="229" t="s">
+    <row r="113" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A113" s="228" t="s">
+        <v>363</v>
+      </c>
+      <c r="B113" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="C113" s="53" t="s">
         <v>365</v>
-      </c>
-      <c r="B113" s="29" t="s">
-        <v>366</v>
-      </c>
-      <c r="C113" s="53" t="s">
-        <v>367</v>
       </c>
       <c r="D113" s="135"/>
       <c r="E113" s="135"/>
@@ -15934,7 +15937,7 @@
         <v>7</v>
       </c>
       <c r="AO113" s="62" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AP113" s="116"/>
       <c r="AQ113" s="116"/>
@@ -15954,13 +15957,13 @@
       <c r="BE113" s="116"/>
       <c r="BF113" s="116"/>
     </row>
-    <row r="114" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="229"/>
+    <row r="114" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A114" s="228"/>
       <c r="B114" s="29" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C114" s="53" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D114" s="135"/>
       <c r="E114" s="135"/>
@@ -16042,7 +16045,7 @@
         <v>140</v>
       </c>
       <c r="AO114" s="62" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AP114" s="116"/>
       <c r="AQ114" s="116"/>
@@ -16062,15 +16065,15 @@
       <c r="BE114" s="116"/>
       <c r="BF114" s="116"/>
     </row>
-    <row r="115" spans="1:58" ht="82.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="222" t="s">
+    <row r="115" spans="1:58" ht="82.95" customHeight="1">
+      <c r="A115" s="230" t="s">
+        <v>370</v>
+      </c>
+      <c r="B115" s="29" t="s">
+        <v>371</v>
+      </c>
+      <c r="C115" s="53" t="s">
         <v>372</v>
-      </c>
-      <c r="B115" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="C115" s="53" t="s">
-        <v>374</v>
       </c>
       <c r="D115" s="135"/>
       <c r="E115" s="135"/>
@@ -16153,7 +16156,7 @@
         <v>12</v>
       </c>
       <c r="AO115" s="62" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AP115" s="116"/>
       <c r="AQ115" s="116"/>
@@ -16173,13 +16176,13 @@
       <c r="BE115" s="116"/>
       <c r="BF115" s="116"/>
     </row>
-    <row r="116" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="222"/>
+    <row r="116" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A116" s="230"/>
       <c r="B116" s="29" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C116" s="53" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D116" s="135"/>
       <c r="E116" s="135"/>
@@ -16262,7 +16265,7 @@
         <v>12000</v>
       </c>
       <c r="AO116" s="62" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AP116" s="116"/>
       <c r="AQ116" s="116"/>
@@ -16282,15 +16285,15 @@
       <c r="BE116" s="116"/>
       <c r="BF116" s="116"/>
     </row>
-    <row r="117" spans="1:58" ht="76.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="222" t="s">
+    <row r="117" spans="1:58" ht="76.2" customHeight="1">
+      <c r="A117" s="230" t="s">
+        <v>377</v>
+      </c>
+      <c r="B117" s="39" t="s">
+        <v>378</v>
+      </c>
+      <c r="C117" s="53" t="s">
         <v>379</v>
-      </c>
-      <c r="B117" s="39" t="s">
-        <v>380</v>
-      </c>
-      <c r="C117" s="53" t="s">
-        <v>381</v>
       </c>
       <c r="D117" s="135"/>
       <c r="E117" s="135"/>
@@ -16373,7 +16376,7 @@
         <v>6</v>
       </c>
       <c r="AO117" s="84" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AP117" s="116"/>
       <c r="AQ117" s="116"/>
@@ -16393,13 +16396,13 @@
       <c r="BE117" s="116"/>
       <c r="BF117" s="116"/>
     </row>
-    <row r="118" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="229"/>
+    <row r="118" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A118" s="228"/>
       <c r="B118" s="39" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C118" s="53" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D118" s="135"/>
       <c r="E118" s="135"/>
@@ -16482,7 +16485,7 @@
         <v>300</v>
       </c>
       <c r="AO118" s="84" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AP118" s="116"/>
       <c r="AQ118" s="116"/>
@@ -16502,15 +16505,15 @@
       <c r="BE118" s="116"/>
       <c r="BF118" s="116"/>
     </row>
-    <row r="119" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="261" t="s">
+    <row r="119" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A119" s="224" t="s">
+        <v>383</v>
+      </c>
+      <c r="B119" s="37" t="s">
+        <v>384</v>
+      </c>
+      <c r="C119" s="53" t="s">
         <v>385</v>
-      </c>
-      <c r="B119" s="37" t="s">
-        <v>386</v>
-      </c>
-      <c r="C119" s="53" t="s">
-        <v>387</v>
       </c>
       <c r="D119" s="135"/>
       <c r="E119" s="135"/>
@@ -16584,7 +16587,7 @@
         <v>0.8</v>
       </c>
       <c r="AO119" s="84" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AP119" s="116"/>
       <c r="AQ119" s="116"/>
@@ -16604,13 +16607,13 @@
       <c r="BE119" s="116"/>
       <c r="BF119" s="116"/>
     </row>
-    <row r="120" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="262"/>
+    <row r="120" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A120" s="234"/>
       <c r="B120" s="37" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C120" s="53" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D120" s="135"/>
       <c r="E120" s="135"/>
@@ -16684,7 +16687,7 @@
         <v>0.8</v>
       </c>
       <c r="AO120" s="84" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AP120" s="116"/>
       <c r="AQ120" s="116"/>
@@ -16704,13 +16707,13 @@
       <c r="BE120" s="116"/>
       <c r="BF120" s="116"/>
     </row>
-    <row r="121" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="241"/>
+    <row r="121" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A121" s="231"/>
       <c r="B121" s="37" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C121" s="53" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D121" s="135"/>
       <c r="E121" s="135"/>
@@ -16784,7 +16787,7 @@
         <v>0.8</v>
       </c>
       <c r="AO121" s="84" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AP121" s="116"/>
       <c r="AQ121" s="116"/>
@@ -16804,15 +16807,15 @@
       <c r="BE121" s="116"/>
       <c r="BF121" s="116"/>
     </row>
-    <row r="122" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="229" t="s">
+    <row r="122" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A122" s="228" t="s">
+        <v>393</v>
+      </c>
+      <c r="B122" s="29" t="s">
+        <v>394</v>
+      </c>
+      <c r="C122" s="53" t="s">
         <v>395</v>
-      </c>
-      <c r="B122" s="29" t="s">
-        <v>396</v>
-      </c>
-      <c r="C122" s="53" t="s">
-        <v>397</v>
       </c>
       <c r="D122" s="135"/>
       <c r="E122" s="135"/>
@@ -16899,7 +16902,7 @@
         <v>6</v>
       </c>
       <c r="AO122" s="62" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AP122" s="116"/>
       <c r="AQ122" s="116"/>
@@ -16919,13 +16922,13 @@
       <c r="BE122" s="116"/>
       <c r="BF122" s="116"/>
     </row>
-    <row r="123" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="229"/>
+    <row r="123" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A123" s="228"/>
       <c r="B123" s="29" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C123" s="53" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D123" s="135"/>
       <c r="E123" s="135"/>
@@ -17012,7 +17015,7 @@
         <v>300</v>
       </c>
       <c r="AO123" s="62" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AP123" s="116"/>
       <c r="AQ123" s="116"/>
@@ -17032,15 +17035,15 @@
       <c r="BE123" s="116"/>
       <c r="BF123" s="116"/>
     </row>
-    <row r="124" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="229" t="s">
+    <row r="124" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A124" s="228" t="s">
+        <v>399</v>
+      </c>
+      <c r="B124" s="29" t="s">
+        <v>400</v>
+      </c>
+      <c r="C124" s="53" t="s">
         <v>401</v>
-      </c>
-      <c r="B124" s="29" t="s">
-        <v>402</v>
-      </c>
-      <c r="C124" s="53" t="s">
-        <v>403</v>
       </c>
       <c r="D124" s="135"/>
       <c r="E124" s="135"/>
@@ -17118,7 +17121,7 @@
         <v>2</v>
       </c>
       <c r="AO124" s="62" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AP124" s="116"/>
       <c r="AQ124" s="116"/>
@@ -17138,13 +17141,13 @@
       <c r="BE124" s="116"/>
       <c r="BF124" s="116"/>
     </row>
-    <row r="125" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="229"/>
+    <row r="125" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A125" s="228"/>
       <c r="B125" s="29" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C125" s="53" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D125" s="135"/>
       <c r="E125" s="135"/>
@@ -17227,7 +17230,7 @@
         <v>160</v>
       </c>
       <c r="AO125" s="62" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AP125" s="116"/>
       <c r="AQ125" s="116"/>
@@ -17247,15 +17250,15 @@
       <c r="BE125" s="116"/>
       <c r="BF125" s="116"/>
     </row>
-    <row r="126" spans="1:58" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:58" ht="77.400000000000006" customHeight="1">
       <c r="A126" s="29" t="s">
+        <v>406</v>
+      </c>
+      <c r="B126" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="C126" s="53" t="s">
         <v>408</v>
-      </c>
-      <c r="B126" s="39" t="s">
-        <v>409</v>
-      </c>
-      <c r="C126" s="53" t="s">
-        <v>410</v>
       </c>
       <c r="D126" s="9" t="s">
         <v>17</v>
@@ -17356,7 +17359,7 @@
         <v>440</v>
       </c>
       <c r="AO126" s="60" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AP126" s="116"/>
       <c r="AQ126" s="116"/>
@@ -17376,15 +17379,15 @@
       <c r="BE126" s="116"/>
       <c r="BF126" s="116"/>
     </row>
-    <row r="127" spans="1:58" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="222" t="s">
+    <row r="127" spans="1:58" ht="99.6" customHeight="1">
+      <c r="A127" s="230" t="s">
+        <v>410</v>
+      </c>
+      <c r="B127" s="29" t="s">
+        <v>411</v>
+      </c>
+      <c r="C127" s="53" t="s">
         <v>412</v>
-      </c>
-      <c r="B127" s="29" t="s">
-        <v>413</v>
-      </c>
-      <c r="C127" s="53" t="s">
-        <v>414</v>
       </c>
       <c r="D127" s="135"/>
       <c r="E127" s="135"/>
@@ -17470,7 +17473,7 @@
         <v>370</v>
       </c>
       <c r="AO127" s="60" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AP127" s="116"/>
       <c r="AQ127" s="116"/>
@@ -17490,13 +17493,13 @@
       <c r="BE127" s="116"/>
       <c r="BF127" s="116"/>
     </row>
-    <row r="128" spans="1:58" ht="98.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="229"/>
+    <row r="128" spans="1:58" ht="98.4" customHeight="1">
+      <c r="A128" s="228"/>
       <c r="B128" s="29" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C128" s="53" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D128" s="9" t="s">
         <v>17</v>
@@ -17581,7 +17584,7 @@
         <v>157</v>
       </c>
       <c r="AO128" s="60" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AP128" s="116"/>
       <c r="AQ128" s="116"/>
@@ -17601,15 +17604,15 @@
       <c r="BE128" s="116"/>
       <c r="BF128" s="116"/>
     </row>
-    <row r="129" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:58" ht="43.5" customHeight="1">
       <c r="A129" s="74" t="s">
+        <v>417</v>
+      </c>
+      <c r="B129" s="39" t="s">
+        <v>418</v>
+      </c>
+      <c r="C129" s="53" t="s">
         <v>419</v>
-      </c>
-      <c r="B129" s="39" t="s">
-        <v>420</v>
-      </c>
-      <c r="C129" s="53" t="s">
-        <v>421</v>
       </c>
       <c r="D129" s="9" t="s">
         <v>17</v>
@@ -17687,7 +17690,7 @@
         <v>0.7</v>
       </c>
       <c r="AO129" s="66" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AP129" s="116"/>
       <c r="AQ129" s="116"/>
@@ -17707,15 +17710,15 @@
       <c r="BE129" s="116"/>
       <c r="BF129" s="116"/>
     </row>
-    <row r="130" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="229" t="s">
+    <row r="130" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A130" s="228" t="s">
+        <v>421</v>
+      </c>
+      <c r="B130" s="39" t="s">
+        <v>422</v>
+      </c>
+      <c r="C130" s="53" t="s">
         <v>423</v>
-      </c>
-      <c r="B130" s="39" t="s">
-        <v>424</v>
-      </c>
-      <c r="C130" s="53" t="s">
-        <v>425</v>
       </c>
       <c r="D130" s="9" t="s">
         <v>17</v>
@@ -17804,7 +17807,7 @@
         <v>1060</v>
       </c>
       <c r="AO130" s="60" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AP130" s="116"/>
       <c r="AQ130" s="116"/>
@@ -17824,13 +17827,13 @@
       <c r="BE130" s="116"/>
       <c r="BF130" s="116"/>
     </row>
-    <row r="131" spans="1:58" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="229"/>
+    <row r="131" spans="1:58" ht="67.95" customHeight="1">
+      <c r="A131" s="228"/>
       <c r="B131" s="39" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C131" s="53" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D131" s="9" t="s">
         <v>17</v>
@@ -17919,7 +17922,7 @@
         <v>1000</v>
       </c>
       <c r="AO131" s="61" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AP131" s="116"/>
       <c r="AQ131" s="116"/>
@@ -17939,15 +17942,15 @@
       <c r="BE131" s="116"/>
       <c r="BF131" s="116"/>
     </row>
-    <row r="132" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="222" t="s">
+    <row r="132" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A132" s="230" t="s">
+        <v>428</v>
+      </c>
+      <c r="B132" s="29" t="s">
+        <v>429</v>
+      </c>
+      <c r="C132" s="53" t="s">
         <v>430</v>
-      </c>
-      <c r="B132" s="29" t="s">
-        <v>431</v>
-      </c>
-      <c r="C132" s="53" t="s">
-        <v>432</v>
       </c>
       <c r="D132" s="9" t="s">
         <v>17</v>
@@ -18013,7 +18016,7 @@
         <v>0.7</v>
       </c>
       <c r="AO132" s="61" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AP132" s="116"/>
       <c r="AQ132" s="116"/>
@@ -18033,13 +18036,13 @@
       <c r="BE132" s="116"/>
       <c r="BF132" s="116"/>
     </row>
-    <row r="133" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="222"/>
+    <row r="133" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A133" s="230"/>
       <c r="B133" s="29" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C133" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D133" s="9" t="s">
         <v>17</v>
@@ -18105,7 +18108,7 @@
         <v>0.7</v>
       </c>
       <c r="AO133" s="61" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AP133" s="116"/>
       <c r="AQ133" s="116"/>
@@ -18125,15 +18128,15 @@
       <c r="BE133" s="116"/>
       <c r="BF133" s="116"/>
     </row>
-    <row r="134" spans="1:58" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="234" t="s">
+    <row r="134" spans="1:58" ht="53.4" customHeight="1">
+      <c r="A134" s="222" t="s">
+        <v>435</v>
+      </c>
+      <c r="B134" s="39" t="s">
+        <v>436</v>
+      </c>
+      <c r="C134" s="53" t="s">
         <v>437</v>
-      </c>
-      <c r="B134" s="39" t="s">
-        <v>438</v>
-      </c>
-      <c r="C134" s="53" t="s">
-        <v>439</v>
       </c>
       <c r="D134" s="9" t="s">
         <v>17</v>
@@ -18209,7 +18212,7 @@
         <v>240</v>
       </c>
       <c r="AO134" s="60" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AP134" s="116"/>
       <c r="AQ134" s="116"/>
@@ -18229,13 +18232,13 @@
       <c r="BE134" s="116"/>
       <c r="BF134" s="116"/>
     </row>
-    <row r="135" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="234"/>
+    <row r="135" spans="1:58" ht="43.5" customHeight="1">
+      <c r="A135" s="222"/>
       <c r="B135" s="39" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C135" s="53" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D135" s="9" t="s">
         <v>17</v>
@@ -18311,7 +18314,7 @@
         <v>4800</v>
       </c>
       <c r="AO135" s="60" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AP135" s="116"/>
       <c r="AQ135" s="116"/>
@@ -18331,9 +18334,9 @@
       <c r="BE135" s="116"/>
       <c r="BF135" s="116"/>
     </row>
-    <row r="136" spans="1:58" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:58" ht="16.2" customHeight="1">
       <c r="A136" s="111" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B136" s="107"/>
       <c r="C136" s="108"/>
@@ -18401,15 +18404,15 @@
       <c r="BE136" s="116"/>
       <c r="BF136" s="116"/>
     </row>
-    <row r="137" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:58" ht="43.5" customHeight="1">
       <c r="A137" s="104" t="s">
+        <v>443</v>
+      </c>
+      <c r="B137" s="105" t="s">
+        <v>444</v>
+      </c>
+      <c r="C137" s="106" t="s">
         <v>445</v>
-      </c>
-      <c r="B137" s="105" t="s">
-        <v>446</v>
-      </c>
-      <c r="C137" s="106" t="s">
-        <v>447</v>
       </c>
       <c r="D137" s="138"/>
       <c r="E137" s="138"/>
@@ -18494,7 +18497,7 @@
         <v>825</v>
       </c>
       <c r="AO137" s="69" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AP137" s="116"/>
       <c r="AQ137" s="116"/>
@@ -18514,15 +18517,15 @@
       <c r="BE137" s="116"/>
       <c r="BF137" s="116"/>
     </row>
-    <row r="138" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:58" ht="43.5" customHeight="1">
       <c r="A138" s="39" t="s">
+        <v>447</v>
+      </c>
+      <c r="B138" s="77" t="s">
+        <v>448</v>
+      </c>
+      <c r="C138" s="78" t="s">
         <v>449</v>
-      </c>
-      <c r="B138" s="77" t="s">
-        <v>450</v>
-      </c>
-      <c r="C138" s="78" t="s">
-        <v>451</v>
       </c>
       <c r="D138" s="135"/>
       <c r="E138" s="135"/>
@@ -18607,7 +18610,7 @@
         <v>1000</v>
       </c>
       <c r="AO138" s="69" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AP138" s="116"/>
       <c r="AQ138" s="116"/>
@@ -18627,15 +18630,15 @@
       <c r="BE138" s="116"/>
       <c r="BF138" s="116"/>
     </row>
-    <row r="139" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:58" ht="43.5" customHeight="1">
       <c r="A139" s="39" t="s">
+        <v>451</v>
+      </c>
+      <c r="B139" s="77" t="s">
+        <v>452</v>
+      </c>
+      <c r="C139" s="78" t="s">
         <v>453</v>
-      </c>
-      <c r="B139" s="77" t="s">
-        <v>454</v>
-      </c>
-      <c r="C139" s="78" t="s">
-        <v>455</v>
       </c>
       <c r="D139" s="135"/>
       <c r="E139" s="135"/>
@@ -18720,7 +18723,7 @@
         <v>849</v>
       </c>
       <c r="AO139" s="69" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AP139" s="116"/>
       <c r="AQ139" s="116"/>
@@ -18740,15 +18743,15 @@
       <c r="BE139" s="116"/>
       <c r="BF139" s="116"/>
     </row>
-    <row r="140" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:58" ht="43.5" customHeight="1">
       <c r="A140" s="39" t="s">
+        <v>455</v>
+      </c>
+      <c r="B140" s="79" t="s">
+        <v>456</v>
+      </c>
+      <c r="C140" s="78" t="s">
         <v>457</v>
-      </c>
-      <c r="B140" s="79" t="s">
-        <v>458</v>
-      </c>
-      <c r="C140" s="78" t="s">
-        <v>459</v>
       </c>
       <c r="D140" s="135"/>
       <c r="E140" s="135"/>
@@ -18831,7 +18834,7 @@
         <v>600</v>
       </c>
       <c r="AO140" s="70" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AP140" s="116"/>
       <c r="AQ140" s="116"/>
@@ -18851,15 +18854,15 @@
       <c r="BE140" s="116"/>
       <c r="BF140" s="116"/>
     </row>
-    <row r="141" spans="1:58" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:58" ht="43.5" customHeight="1" thickBot="1">
       <c r="A141" s="39" t="s">
+        <v>459</v>
+      </c>
+      <c r="B141" s="77" t="s">
+        <v>460</v>
+      </c>
+      <c r="C141" s="78" t="s">
         <v>461</v>
-      </c>
-      <c r="B141" s="77" t="s">
-        <v>462</v>
-      </c>
-      <c r="C141" s="78" t="s">
-        <v>463</v>
       </c>
       <c r="D141" s="135"/>
       <c r="E141" s="135"/>
@@ -18944,7 +18947,7 @@
         <v>455</v>
       </c>
       <c r="AO141" s="71" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AP141" s="116"/>
       <c r="AQ141" s="116"/>
@@ -18964,15 +18967,15 @@
       <c r="BE141" s="116"/>
       <c r="BF141" s="116"/>
     </row>
-    <row r="142" spans="1:58" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:58" ht="43.5" customHeight="1" thickBot="1">
       <c r="A142" s="39" t="s">
+        <v>463</v>
+      </c>
+      <c r="B142" s="217" t="s">
+        <v>464</v>
+      </c>
+      <c r="C142" s="218" t="s">
         <v>465</v>
-      </c>
-      <c r="B142" s="217" t="s">
-        <v>466</v>
-      </c>
-      <c r="C142" s="218" t="s">
-        <v>467</v>
       </c>
       <c r="D142" s="135"/>
       <c r="E142" s="135"/>
@@ -19036,7 +19039,7 @@
         <v>1</v>
       </c>
       <c r="AO142" s="71" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AP142" s="116"/>
       <c r="AQ142" s="116"/>
@@ -19056,7 +19059,7 @@
       <c r="BE142" s="116"/>
       <c r="BF142" s="116"/>
     </row>
-    <row r="143" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:58" ht="43.5" customHeight="1">
       <c r="A143" s="129"/>
       <c r="B143" s="116"/>
       <c r="C143" s="116"/>
@@ -19116,7 +19119,7 @@
       <c r="BE143" s="116"/>
       <c r="BF143" s="116"/>
     </row>
-    <row r="144" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:58" ht="43.5" customHeight="1">
       <c r="A144" s="129"/>
       <c r="B144" s="116"/>
       <c r="C144" s="116"/>
@@ -19176,7 +19179,7 @@
       <c r="BE144" s="116"/>
       <c r="BF144" s="116"/>
     </row>
-    <row r="145" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:58" ht="43.5" customHeight="1">
       <c r="A145" s="129"/>
       <c r="B145" s="116"/>
       <c r="C145" s="116"/>
@@ -19236,7 +19239,7 @@
       <c r="BE145" s="116"/>
       <c r="BF145" s="116"/>
     </row>
-    <row r="146" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:58" ht="43.5" customHeight="1">
       <c r="A146" s="129"/>
       <c r="B146" s="116"/>
       <c r="C146" s="116"/>
@@ -19296,7 +19299,7 @@
       <c r="BE146" s="116"/>
       <c r="BF146" s="116"/>
     </row>
-    <row r="147" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:58" ht="43.5" customHeight="1">
       <c r="A147" s="129"/>
       <c r="B147" s="116"/>
       <c r="C147" s="116"/>
@@ -19356,7 +19359,7 @@
       <c r="BE147" s="116"/>
       <c r="BF147" s="116"/>
     </row>
-    <row r="148" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:58" ht="43.5" customHeight="1">
       <c r="A148" s="132"/>
       <c r="B148" s="116"/>
       <c r="C148" s="116"/>
@@ -19416,7 +19419,7 @@
       <c r="BE148" s="116"/>
       <c r="BF148" s="116"/>
     </row>
-    <row r="149" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:58" ht="43.5" customHeight="1">
       <c r="A149" s="132"/>
       <c r="B149" s="116"/>
       <c r="C149" s="116"/>
@@ -19476,7 +19479,7 @@
       <c r="BE149" s="116"/>
       <c r="BF149" s="116"/>
     </row>
-    <row r="150" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:58" ht="43.5" customHeight="1">
       <c r="A150" s="133"/>
       <c r="B150" s="116"/>
       <c r="C150" s="116"/>
@@ -19536,7 +19539,7 @@
       <c r="BE150" s="116"/>
       <c r="BF150" s="116"/>
     </row>
-    <row r="151" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:58" ht="43.5" customHeight="1">
       <c r="A151" s="133"/>
       <c r="B151" s="116"/>
       <c r="C151" s="116"/>
@@ -19596,7 +19599,7 @@
       <c r="BE151" s="116"/>
       <c r="BF151" s="116"/>
     </row>
-    <row r="152" spans="1:58" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:58" ht="43.5" customHeight="1">
       <c r="A152" s="133"/>
       <c r="B152" s="116"/>
       <c r="C152" s="116"/>
@@ -19657,43 +19660,8 @@
       <c r="BF152" s="116"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="MZNFbxzz2/HCMe/vUn4I7zMAcKMM2kHoG3KwocFq10m0xSTxu80AGOsAFxVjiYagbLKeGxjJfnWAPiknog8BQw==" saltValue="2hbpJChDnOW/peDO9z7CRw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <autoFilter ref="A8:BF142" xr:uid="{FF0FD833-DA25-49DC-8173-D7C8564C9878}"/>
   <mergeCells count="50">
-    <mergeCell ref="A60:A62"/>
-    <mergeCell ref="A37:A39"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="A42:A46"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="A117:A118"/>
-    <mergeCell ref="A119:A121"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A127:A128"/>
-    <mergeCell ref="A111:A112"/>
-    <mergeCell ref="A113:A114"/>
-    <mergeCell ref="A115:A116"/>
-    <mergeCell ref="A106:A110"/>
-    <mergeCell ref="A84:A89"/>
-    <mergeCell ref="A90:A95"/>
-    <mergeCell ref="A96:A98"/>
-    <mergeCell ref="A105:B105"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="H7:L7"/>
-    <mergeCell ref="M7:Q7"/>
-    <mergeCell ref="R7:V7"/>
-    <mergeCell ref="W7:AA7"/>
-    <mergeCell ref="H6:Q6"/>
-    <mergeCell ref="R6:AA6"/>
-    <mergeCell ref="AL6:AN7"/>
-    <mergeCell ref="AB6:AK6"/>
-    <mergeCell ref="AB7:AF7"/>
-    <mergeCell ref="AG7:AK7"/>
     <mergeCell ref="A82:A83"/>
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="D7:G7"/>
@@ -19710,6 +19678,40 @@
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="A63:B63"/>
     <mergeCell ref="A34:B34"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="H7:L7"/>
+    <mergeCell ref="M7:Q7"/>
+    <mergeCell ref="R7:V7"/>
+    <mergeCell ref="W7:AA7"/>
+    <mergeCell ref="H6:Q6"/>
+    <mergeCell ref="R6:AA6"/>
+    <mergeCell ref="AL6:AN7"/>
+    <mergeCell ref="AB6:AK6"/>
+    <mergeCell ref="AB7:AF7"/>
+    <mergeCell ref="AG7:AK7"/>
+    <mergeCell ref="A111:A112"/>
+    <mergeCell ref="A113:A114"/>
+    <mergeCell ref="A115:A116"/>
+    <mergeCell ref="A106:A110"/>
+    <mergeCell ref="A84:A89"/>
+    <mergeCell ref="A90:A95"/>
+    <mergeCell ref="A96:A98"/>
+    <mergeCell ref="A105:B105"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="A119:A121"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A127:A128"/>
+    <mergeCell ref="A60:A62"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="A42:A46"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A52:B52"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19735,15 +19737,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010032D42CB87088684C8C55529ACA400833" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="116a614d5496bbbd47bb867636028f47">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="059fd7f8-59e3-4ad4-b295-2c7569ffaa28" xmlns:ns3="e689b4b5-7069-4f87-a0fb-7ffa9fc42158" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2fda7db35d65f605230d67fc195a5aa9" ns2:_="" ns3:_="">
     <xsd:import namespace="059fd7f8-59e3-4ad4-b295-2c7569ffaa28"/>
@@ -19966,6 +19959,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4441BF8-F257-49EE-99C1-FF4F670D09C3}">
   <ds:schemaRefs>
@@ -19984,14 +19986,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A8ABC59-4B92-499E-809B-1276582C514D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5A2E045-8194-4DF4-AF94-5B802E4F288D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20008,4 +20002,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A8ABC59-4B92-499E-809B-1276582C514D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>